--- a/data/themes/books/books.xlsx
+++ b/data/themes/books/books.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C801"/>
+  <dimension ref="A1:D1184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -437,6 +437,11 @@
           <t>year</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>only_list</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12436,6 +12441,6900 @@
       </c>
       <c r="C801" t="n">
         <v>1948</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>Фёдор Достоевский</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Двойник</t>
+        </is>
+      </c>
+      <c r="C802" t="n">
+        <v>1846</v>
+      </c>
+      <c r="D802" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>Фёдор Достоевский</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Село Степанчиково и его обитатели</t>
+        </is>
+      </c>
+      <c r="C803" t="n">
+        <v>1859</v>
+      </c>
+      <c r="D803" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>Фёдор Достоевский</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Неточка Незванова</t>
+        </is>
+      </c>
+      <c r="C804" t="n">
+        <v>1849</v>
+      </c>
+      <c r="D804" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>Фёдор Достоевский</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Вечный муж</t>
+        </is>
+      </c>
+      <c r="C805" t="n">
+        <v>1870</v>
+      </c>
+      <c r="D805" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>Фёдор Достоевский</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Хозяйка</t>
+        </is>
+      </c>
+      <c r="C806" t="n">
+        <v>1847</v>
+      </c>
+      <c r="D806" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>Лев Толстой</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Семейное счастие</t>
+        </is>
+      </c>
+      <c r="C807" t="n">
+        <v>1859</v>
+      </c>
+      <c r="D807" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>Лев Толстой</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Утро помещика</t>
+        </is>
+      </c>
+      <c r="C808" t="n">
+        <v>1856</v>
+      </c>
+      <c r="D808" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>Лев Толстой</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Холстомер</t>
+        </is>
+      </c>
+      <c r="C809" t="n">
+        <v>1886</v>
+      </c>
+      <c r="D809" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>Лев Толстой</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Отец Сергий</t>
+        </is>
+      </c>
+      <c r="C810" t="n">
+        <v>1912</v>
+      </c>
+      <c r="D810" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>Лев Толстой</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Дьявол</t>
+        </is>
+      </c>
+      <c r="C811" t="n">
+        <v>1911</v>
+      </c>
+      <c r="D811" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>Иван Тургенев</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Первая любовь</t>
+        </is>
+      </c>
+      <c r="C812" t="n">
+        <v>1860</v>
+      </c>
+      <c r="D812" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>Иван Тургенев</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Муму</t>
+        </is>
+      </c>
+      <c r="C813" t="n">
+        <v>1854</v>
+      </c>
+      <c r="D813" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>Иван Тургенев</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Ася</t>
+        </is>
+      </c>
+      <c r="C814" t="n">
+        <v>1858</v>
+      </c>
+      <c r="D814" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>Иван Тургенев</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Вешние воды</t>
+        </is>
+      </c>
+      <c r="C815" t="n">
+        <v>1872</v>
+      </c>
+      <c r="D815" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>Иван Тургенев</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Постоялый двор</t>
+        </is>
+      </c>
+      <c r="C816" t="n">
+        <v>1855</v>
+      </c>
+      <c r="D816" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>Иван Тургенев</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Бежин луг</t>
+        </is>
+      </c>
+      <c r="C817" t="n">
+        <v>1851</v>
+      </c>
+      <c r="D817" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>Иван Тургенев</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Призраки</t>
+        </is>
+      </c>
+      <c r="C818" t="n">
+        <v>1864</v>
+      </c>
+      <c r="D818" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>Михаил Булгаков</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Записки юного врача</t>
+        </is>
+      </c>
+      <c r="C819" t="n">
+        <v>1926</v>
+      </c>
+      <c r="D819" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>Михаил Булгаков</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Морфий</t>
+        </is>
+      </c>
+      <c r="C820" t="n">
+        <v>1927</v>
+      </c>
+      <c r="D820" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>Михаил Булгаков</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Дни Турбиных</t>
+        </is>
+      </c>
+      <c r="C821" t="n">
+        <v>1926</v>
+      </c>
+      <c r="D821" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>Михаил Булгаков</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Зойкина квартира</t>
+        </is>
+      </c>
+      <c r="C822" t="n">
+        <v>1926</v>
+      </c>
+      <c r="D822" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>Михаил Булгаков</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Багровый остров</t>
+        </is>
+      </c>
+      <c r="C823" t="n">
+        <v>1928</v>
+      </c>
+      <c r="D823" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>Михаил Булгаков</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Жизнь господина де Мольера</t>
+        </is>
+      </c>
+      <c r="C824" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D824" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>Михаил Булгаков</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Адам и Ева</t>
+        </is>
+      </c>
+      <c r="C825" t="n">
+        <v>1931</v>
+      </c>
+      <c r="D825" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>Михаил Булгаков</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Ханский огонь</t>
+        </is>
+      </c>
+      <c r="C826" t="n">
+        <v>1924</v>
+      </c>
+      <c r="D826" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>Братья Стругацкие</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Волны гасят ветер</t>
+        </is>
+      </c>
+      <c r="C827" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D827" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>Братья Стругацкие</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Отягощённые злом, или Сорок лет спустя</t>
+        </is>
+      </c>
+      <c r="C828" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D828" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>Братья Стругацкие</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Гадкие лебеди</t>
+        </is>
+      </c>
+      <c r="C829" t="n">
+        <v>1972</v>
+      </c>
+      <c r="D829" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>Братья Стругацкие</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Малыш</t>
+        </is>
+      </c>
+      <c r="C830" t="n">
+        <v>1971</v>
+      </c>
+      <c r="D830" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>Братья Стругацкие</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Далёкая Радуга</t>
+        </is>
+      </c>
+      <c r="C831" t="n">
+        <v>1963</v>
+      </c>
+      <c r="D831" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>Братья Стругацкие</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Страна багровых туч</t>
+        </is>
+      </c>
+      <c r="C832" t="n">
+        <v>1959</v>
+      </c>
+      <c r="D832" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>Братья Стругацкие</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Хромая судьба</t>
+        </is>
+      </c>
+      <c r="C833" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D833" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>Чарльз Диккенс</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Приключения Оливера Твиста</t>
+        </is>
+      </c>
+      <c r="C834" t="n">
+        <v>1838</v>
+      </c>
+      <c r="D834" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>Чарльз Диккенс</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Дэвид Копперфилд</t>
+        </is>
+      </c>
+      <c r="C835" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D835" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>Чарльз Диккенс</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Холодный дом</t>
+        </is>
+      </c>
+      <c r="C836" t="n">
+        <v>1853</v>
+      </c>
+      <c r="D836" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>Чарльз Диккенс</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Посмертные записки Пиквикского клуба</t>
+        </is>
+      </c>
+      <c r="C837" t="n">
+        <v>1837</v>
+      </c>
+      <c r="D837" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>Чарльз Диккенс</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Лавка древностей</t>
+        </is>
+      </c>
+      <c r="C838" t="n">
+        <v>1841</v>
+      </c>
+      <c r="D838" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>Чарльз Диккенс</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Домби и сын</t>
+        </is>
+      </c>
+      <c r="C839" t="n">
+        <v>1848</v>
+      </c>
+      <c r="D839" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>Чарльз Диккенс</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>Наш общий друг</t>
+        </is>
+      </c>
+      <c r="C840" t="n">
+        <v>1865</v>
+      </c>
+      <c r="D840" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>Чарльз Диккенс</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>Тяжёлые времена</t>
+        </is>
+      </c>
+      <c r="C841" t="n">
+        <v>1854</v>
+      </c>
+      <c r="D841" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>Чарльз Диккенс</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Тайна Эдвина Друда</t>
+        </is>
+      </c>
+      <c r="C842" t="n">
+        <v>1870</v>
+      </c>
+      <c r="D842" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>Чарльз Диккенс</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Барнеби Радж</t>
+        </is>
+      </c>
+      <c r="C843" t="n">
+        <v>1841</v>
+      </c>
+      <c r="D843" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>Чарльз Диккенс</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Мартин Чезлвит</t>
+        </is>
+      </c>
+      <c r="C844" t="n">
+        <v>1844</v>
+      </c>
+      <c r="D844" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>Александр Дюма</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Графиня де Монсоро</t>
+        </is>
+      </c>
+      <c r="C845" t="n">
+        <v>1846</v>
+      </c>
+      <c r="D845" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>Александр Дюма</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Чёрный тюльпан</t>
+        </is>
+      </c>
+      <c r="C846" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D846" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>Александр Дюма</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Джузеппе Бальзамо</t>
+        </is>
+      </c>
+      <c r="C847" t="n">
+        <v>1849</v>
+      </c>
+      <c r="D847" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>Александр Дюма</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Ожерелье королевы</t>
+        </is>
+      </c>
+      <c r="C848" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D848" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>Александр Дюма</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Шевалье де Мезон-Руж</t>
+        </is>
+      </c>
+      <c r="C849" t="n">
+        <v>1845</v>
+      </c>
+      <c r="D849" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>Александр Дюма</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Асканио</t>
+        </is>
+      </c>
+      <c r="C850" t="n">
+        <v>1843</v>
+      </c>
+      <c r="D850" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>Александр Дюма</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Анж Питу</t>
+        </is>
+      </c>
+      <c r="C851" t="n">
+        <v>1851</v>
+      </c>
+      <c r="D851" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>Александр Дюма</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Графиня де Шарни</t>
+        </is>
+      </c>
+      <c r="C852" t="n">
+        <v>1853</v>
+      </c>
+      <c r="D852" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>Александр Дюма</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Две Дианы</t>
+        </is>
+      </c>
+      <c r="C853" t="n">
+        <v>1846</v>
+      </c>
+      <c r="D853" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>Виктор Гюго</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Последний день приговорённого к смерти</t>
+        </is>
+      </c>
+      <c r="C854" t="n">
+        <v>1829</v>
+      </c>
+      <c r="D854" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>Виктор Гюго</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Бюг-Жаргаль</t>
+        </is>
+      </c>
+      <c r="C855" t="n">
+        <v>1826</v>
+      </c>
+      <c r="D855" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>Виктор Гюго</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>Гань Исландец</t>
+        </is>
+      </c>
+      <c r="C856" t="n">
+        <v>1823</v>
+      </c>
+      <c r="D856" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>Виктор Гюго</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Клод Ге</t>
+        </is>
+      </c>
+      <c r="C857" t="n">
+        <v>1834</v>
+      </c>
+      <c r="D857" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>Оноре де Бальзак</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Кузина Бетта</t>
+        </is>
+      </c>
+      <c r="C858" t="n">
+        <v>1846</v>
+      </c>
+      <c r="D858" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>Оноре де Бальзак</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Кузен Понс</t>
+        </is>
+      </c>
+      <c r="C859" t="n">
+        <v>1847</v>
+      </c>
+      <c r="D859" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>Оноре де Бальзак</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Лилия в долине</t>
+        </is>
+      </c>
+      <c r="C860" t="n">
+        <v>1835</v>
+      </c>
+      <c r="D860" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>Оноре де Бальзак</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>Тридцатилетняя женщина</t>
+        </is>
+      </c>
+      <c r="C861" t="n">
+        <v>1842</v>
+      </c>
+      <c r="D861" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>Оноре де Бальзак</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>Шуаны</t>
+        </is>
+      </c>
+      <c r="C862" t="n">
+        <v>1829</v>
+      </c>
+      <c r="D862" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>Оноре де Бальзак</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Сельский врач</t>
+        </is>
+      </c>
+      <c r="C863" t="n">
+        <v>1833</v>
+      </c>
+      <c r="D863" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>Оноре де Бальзак</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Златоокая девушка</t>
+        </is>
+      </c>
+      <c r="C864" t="n">
+        <v>1835</v>
+      </c>
+      <c r="D864" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>Оноре де Бальзак</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Банкирский дом Нусингена</t>
+        </is>
+      </c>
+      <c r="C865" t="n">
+        <v>1838</v>
+      </c>
+      <c r="D865" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>Оноре де Бальзак</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Модеста Миньон</t>
+        </is>
+      </c>
+      <c r="C866" t="n">
+        <v>1844</v>
+      </c>
+      <c r="D866" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>Эмиль Золя</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>Человек-зверь</t>
+        </is>
+      </c>
+      <c r="C867" t="n">
+        <v>1890</v>
+      </c>
+      <c r="D867" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>Эмиль Золя</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Творчество</t>
+        </is>
+      </c>
+      <c r="C868" t="n">
+        <v>1886</v>
+      </c>
+      <c r="D868" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>Эмиль Золя</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Земля</t>
+        </is>
+      </c>
+      <c r="C869" t="n">
+        <v>1887</v>
+      </c>
+      <c r="D869" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>Эмиль Золя</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Карьера Ругонов</t>
+        </is>
+      </c>
+      <c r="C870" t="n">
+        <v>1871</v>
+      </c>
+      <c r="D870" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>Эмиль Золя</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Добыча</t>
+        </is>
+      </c>
+      <c r="C871" t="n">
+        <v>1871</v>
+      </c>
+      <c r="D871" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>Эмиль Золя</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Разгром</t>
+        </is>
+      </c>
+      <c r="C872" t="n">
+        <v>1892</v>
+      </c>
+      <c r="D872" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>Эмиль Золя</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Доктор Паскаль</t>
+        </is>
+      </c>
+      <c r="C873" t="n">
+        <v>1893</v>
+      </c>
+      <c r="D873" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>Эмиль Золя</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Радость жизни</t>
+        </is>
+      </c>
+      <c r="C874" t="n">
+        <v>1884</v>
+      </c>
+      <c r="D874" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>Эмиль Золя</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Деньги</t>
+        </is>
+      </c>
+      <c r="C875" t="n">
+        <v>1891</v>
+      </c>
+      <c r="D875" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>Жюль Верн</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Пять недель на воздушном шаре</t>
+        </is>
+      </c>
+      <c r="C876" t="n">
+        <v>1863</v>
+      </c>
+      <c r="D876" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>Жюль Верн</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>Вокруг Луны</t>
+        </is>
+      </c>
+      <c r="C877" t="n">
+        <v>1869</v>
+      </c>
+      <c r="D877" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>Жюль Верн</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Михаил Строгов</t>
+        </is>
+      </c>
+      <c r="C878" t="n">
+        <v>1876</v>
+      </c>
+      <c r="D878" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>Жюль Верн</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Два года каникул</t>
+        </is>
+      </c>
+      <c r="C879" t="n">
+        <v>1888</v>
+      </c>
+      <c r="D879" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>Жюль Верн</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Робур-завоеватель</t>
+        </is>
+      </c>
+      <c r="C880" t="n">
+        <v>1886</v>
+      </c>
+      <c r="D880" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>Жюль Верн</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Властелин мира</t>
+        </is>
+      </c>
+      <c r="C881" t="n">
+        <v>1904</v>
+      </c>
+      <c r="D881" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>Жюль Верн</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Плавающий остров</t>
+        </is>
+      </c>
+      <c r="C882" t="n">
+        <v>1895</v>
+      </c>
+      <c r="D882" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>Жюль Верн</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Пятьсот миллионов бегумы</t>
+        </is>
+      </c>
+      <c r="C883" t="n">
+        <v>1879</v>
+      </c>
+      <c r="D883" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>Артур Конан Дойл</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Долина ужаса</t>
+        </is>
+      </c>
+      <c r="C884" t="n">
+        <v>1915</v>
+      </c>
+      <c r="D884" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>Артур Конан Дойл</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Ядовитый пояс</t>
+        </is>
+      </c>
+      <c r="C885" t="n">
+        <v>1913</v>
+      </c>
+      <c r="D885" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>Артур Конан Дойл</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Белый отряд</t>
+        </is>
+      </c>
+      <c r="C886" t="n">
+        <v>1891</v>
+      </c>
+      <c r="D886" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>Артур Конан Дойл</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Сэр Найджел</t>
+        </is>
+      </c>
+      <c r="C887" t="n">
+        <v>1906</v>
+      </c>
+      <c r="D887" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>Артур Конан Дойл</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Маракотова бездна</t>
+        </is>
+      </c>
+      <c r="C888" t="n">
+        <v>1929</v>
+      </c>
+      <c r="D888" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>Артур Конан Дойл</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Родни Стоун</t>
+        </is>
+      </c>
+      <c r="C889" t="n">
+        <v>1896</v>
+      </c>
+      <c r="D889" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>Артур Конан Дойл</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Его прощальный поклон</t>
+        </is>
+      </c>
+      <c r="C890" t="n">
+        <v>1917</v>
+      </c>
+      <c r="D890" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>Артур Конан Дойл</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Архив Шерлока Холмса</t>
+        </is>
+      </c>
+      <c r="C891" t="n">
+        <v>1927</v>
+      </c>
+      <c r="D891" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>Агата Кристи</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>ABC убийства</t>
+        </is>
+      </c>
+      <c r="C892" t="n">
+        <v>1936</v>
+      </c>
+      <c r="D892" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>Агата Кристи</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Объявлено убийство</t>
+        </is>
+      </c>
+      <c r="C893" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D893" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>Агата Кристи</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Зло под солнцем</t>
+        </is>
+      </c>
+      <c r="C894" t="n">
+        <v>1941</v>
+      </c>
+      <c r="D894" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>Агата Кристи</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Свидание со смертью</t>
+        </is>
+      </c>
+      <c r="C895" t="n">
+        <v>1938</v>
+      </c>
+      <c r="D895" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>Агата Кристи</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Пять поросят</t>
+        </is>
+      </c>
+      <c r="C896" t="n">
+        <v>1942</v>
+      </c>
+      <c r="D896" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>Агата Кристи</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Занавес</t>
+        </is>
+      </c>
+      <c r="C897" t="n">
+        <v>1975</v>
+      </c>
+      <c r="D897" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>Агата Кристи</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Убийство в Месопотамии</t>
+        </is>
+      </c>
+      <c r="C898" t="n">
+        <v>1936</v>
+      </c>
+      <c r="D898" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>Агата Кристи</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>В 4.50 из Паддингтона</t>
+        </is>
+      </c>
+      <c r="C899" t="n">
+        <v>1957</v>
+      </c>
+      <c r="D899" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>Агата Кристи</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Карибская тайна</t>
+        </is>
+      </c>
+      <c r="C900" t="n">
+        <v>1964</v>
+      </c>
+      <c r="D900" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>Эрнест Хемингуэй</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Острова в океане</t>
+        </is>
+      </c>
+      <c r="C901" t="n">
+        <v>1970</v>
+      </c>
+      <c r="D901" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>Эрнест Хемингуэй</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>За рекой, в тени деревьев</t>
+        </is>
+      </c>
+      <c r="C902" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D902" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>Эрнест Хемингуэй</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Зелёные холмы Африки</t>
+        </is>
+      </c>
+      <c r="C903" t="n">
+        <v>1935</v>
+      </c>
+      <c r="D903" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>Эрнест Хемингуэй</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Райский сад</t>
+        </is>
+      </c>
+      <c r="C904" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D904" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>Эрих Мария Ремарк</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Возвращение</t>
+        </is>
+      </c>
+      <c r="C905" t="n">
+        <v>1931</v>
+      </c>
+      <c r="D905" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>Эрих Мария Ремарк</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Искра жизни</t>
+        </is>
+      </c>
+      <c r="C906" t="n">
+        <v>1952</v>
+      </c>
+      <c r="D906" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>Эрих Мария Ремарк</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Любите ближнего своего</t>
+        </is>
+      </c>
+      <c r="C907" t="n">
+        <v>1941</v>
+      </c>
+      <c r="D907" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>Эрих Мария Ремарк</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Тени в раю</t>
+        </is>
+      </c>
+      <c r="C908" t="n">
+        <v>1971</v>
+      </c>
+      <c r="D908" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>Эрих Мария Ремарк</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Земля обетованная</t>
+        </is>
+      </c>
+      <c r="C909" t="n">
+        <v>1998</v>
+      </c>
+      <c r="D909" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>Эрих Мария Ремарк</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Станция на горизонте</t>
+        </is>
+      </c>
+      <c r="C910" t="n">
+        <v>1928</v>
+      </c>
+      <c r="D910" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>Эрих Мария Ремарк</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Гэм</t>
+        </is>
+      </c>
+      <c r="C911" t="n">
+        <v>1924</v>
+      </c>
+      <c r="D911" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>Стивен Кинг</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Мёртвая зона</t>
+        </is>
+      </c>
+      <c r="C912" t="n">
+        <v>1979</v>
+      </c>
+      <c r="D912" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>Стивен Кинг</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Зелёная миля</t>
+        </is>
+      </c>
+      <c r="C913" t="n">
+        <v>1996</v>
+      </c>
+      <c r="D913" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>Стивен Кинг</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>11/22/63</t>
+        </is>
+      </c>
+      <c r="C914" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D914" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>Стивен Кинг</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Под куполом</t>
+        </is>
+      </c>
+      <c r="C915" t="n">
+        <v>2009</v>
+      </c>
+      <c r="D915" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>Стивен Кинг</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Жребий</t>
+        </is>
+      </c>
+      <c r="C916" t="n">
+        <v>1975</v>
+      </c>
+      <c r="D916" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>Стивен Кинг</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Кристина</t>
+        </is>
+      </c>
+      <c r="C917" t="n">
+        <v>1983</v>
+      </c>
+      <c r="D917" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>Стивен Кинг</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Куджо</t>
+        </is>
+      </c>
+      <c r="C918" t="n">
+        <v>1981</v>
+      </c>
+      <c r="D918" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>Стивен Кинг</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Мешок с костями</t>
+        </is>
+      </c>
+      <c r="C919" t="n">
+        <v>1998</v>
+      </c>
+      <c r="D919" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>Стивен Кинг</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Мистер Мерседес</t>
+        </is>
+      </c>
+      <c r="C920" t="n">
+        <v>2014</v>
+      </c>
+      <c r="D920" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>Харуки Мураками</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Дэнс, дэнс, дэнс</t>
+        </is>
+      </c>
+      <c r="C921" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D921" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>Харуки Мураками</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>К югу от границы, на запад от солнца</t>
+        </is>
+      </c>
+      <c r="C922" t="n">
+        <v>1992</v>
+      </c>
+      <c r="D922" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>Харуки Мураками</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Спутник любви</t>
+        </is>
+      </c>
+      <c r="C923" t="n">
+        <v>1999</v>
+      </c>
+      <c r="D923" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>Харуки Мураками</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Бесцветный Цукуру Тадзаки и годы его странствий</t>
+        </is>
+      </c>
+      <c r="C924" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D924" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>Харуки Мураками</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Убийство Командора</t>
+        </is>
+      </c>
+      <c r="C925" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D925" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>Харуки Мураками</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Слушай песню ветра</t>
+        </is>
+      </c>
+      <c r="C926" t="n">
+        <v>1979</v>
+      </c>
+      <c r="D926" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>Харуки Мураками</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Пинбол-1973</t>
+        </is>
+      </c>
+      <c r="C927" t="n">
+        <v>1980</v>
+      </c>
+      <c r="D927" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>Харуки Мураками</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>После наступления темноты</t>
+        </is>
+      </c>
+      <c r="C928" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D928" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>Харуки Мураками</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Город и его непостоянные стены</t>
+        </is>
+      </c>
+      <c r="C929" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D929" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>Айзек Азимов</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Второе Основание</t>
+        </is>
+      </c>
+      <c r="C930" t="n">
+        <v>1953</v>
+      </c>
+      <c r="D930" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>Айзек Азимов</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Край Основания</t>
+        </is>
+      </c>
+      <c r="C931" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D931" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>Айзек Азимов</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Основание и Земля</t>
+        </is>
+      </c>
+      <c r="C932" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D932" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>Айзек Азимов</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Обнажённое солнце</t>
+        </is>
+      </c>
+      <c r="C933" t="n">
+        <v>1957</v>
+      </c>
+      <c r="D933" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>Айзек Азимов</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Роботы утренней зари</t>
+        </is>
+      </c>
+      <c r="C934" t="n">
+        <v>1983</v>
+      </c>
+      <c r="D934" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>Айзек Азимов</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Роботы и Империя</t>
+        </is>
+      </c>
+      <c r="C935" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D935" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>Айзек Азимов</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Космические течения</t>
+        </is>
+      </c>
+      <c r="C936" t="n">
+        <v>1952</v>
+      </c>
+      <c r="D936" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>Айзек Азимов</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Камешек в небе</t>
+        </is>
+      </c>
+      <c r="C937" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D937" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>Айзек Азимов</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Фантастическое путешествие</t>
+        </is>
+      </c>
+      <c r="C938" t="n">
+        <v>1966</v>
+      </c>
+      <c r="D938" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>Роберт Хайнлайн</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Двойная звезда</t>
+        </is>
+      </c>
+      <c r="C939" t="n">
+        <v>1956</v>
+      </c>
+      <c r="D939" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>Роберт Хайнлайн</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>Дверь в лето</t>
+        </is>
+      </c>
+      <c r="C940" t="n">
+        <v>1957</v>
+      </c>
+      <c r="D940" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>Роберт Хайнлайн</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>Достаточно времени для любви</t>
+        </is>
+      </c>
+      <c r="C941" t="n">
+        <v>1973</v>
+      </c>
+      <c r="D941" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>Роберт Хайнлайн</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>Туннель в небе</t>
+        </is>
+      </c>
+      <c r="C942" t="n">
+        <v>1955</v>
+      </c>
+      <c r="D942" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>Роберт Хайнлайн</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>Кукловоды</t>
+        </is>
+      </c>
+      <c r="C943" t="n">
+        <v>1951</v>
+      </c>
+      <c r="D943" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>Роберт Хайнлайн</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Пятница</t>
+        </is>
+      </c>
+      <c r="C944" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D944" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>Роберт Хайнлайн</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>Гражданин Галактики</t>
+        </is>
+      </c>
+      <c r="C945" t="n">
+        <v>1957</v>
+      </c>
+      <c r="D945" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>Роберт Хайнлайн</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>Число зверя</t>
+        </is>
+      </c>
+      <c r="C946" t="n">
+        <v>1980</v>
+      </c>
+      <c r="D946" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>Роберт Хайнлайн</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>Не убоюсь я зла</t>
+        </is>
+      </c>
+      <c r="C947" t="n">
+        <v>1970</v>
+      </c>
+      <c r="D947" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>Роберт Хайнлайн</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Фермер в небе</t>
+        </is>
+      </c>
+      <c r="C948" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D948" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>Роберт Хайнлайн</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Красная планета</t>
+        </is>
+      </c>
+      <c r="C949" t="n">
+        <v>1949</v>
+      </c>
+      <c r="D949" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>Роберт Хайнлайн</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>Марсианка Подкейн</t>
+        </is>
+      </c>
+      <c r="C950" t="n">
+        <v>1963</v>
+      </c>
+      <c r="D950" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>Виктор Пелевин</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>Ампир В</t>
+        </is>
+      </c>
+      <c r="C951" t="n">
+        <v>2006</v>
+      </c>
+      <c r="D951" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>Виктор Пелевин</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="C952" t="n">
+        <v>2009</v>
+      </c>
+      <c r="D952" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>Виктор Пелевин</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>S.N.U.F.F.</t>
+        </is>
+      </c>
+      <c r="C953" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D953" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>Виктор Пелевин</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>Бэтман Аполло</t>
+        </is>
+      </c>
+      <c r="C954" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D954" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>Виктор Пелевин</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Любовь к трём цукербринам</t>
+        </is>
+      </c>
+      <c r="C955" t="n">
+        <v>2014</v>
+      </c>
+      <c r="D955" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>Виктор Пелевин</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>Смотритель</t>
+        </is>
+      </c>
+      <c r="C956" t="n">
+        <v>2015</v>
+      </c>
+      <c r="D956" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>Виктор Пелевин</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>iPhuck 10</t>
+        </is>
+      </c>
+      <c r="C957" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D957" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>Виктор Пелевин</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Тайные виды на гору Фудзи</t>
+        </is>
+      </c>
+      <c r="C958" t="n">
+        <v>2018</v>
+      </c>
+      <c r="D958" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>Виктор Пелевин</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>KGBT+</t>
+        </is>
+      </c>
+      <c r="C959" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D959" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>Виктор Пелевин</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>Transhumanism Inc.</t>
+        </is>
+      </c>
+      <c r="C960" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D960" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>Борис Акунин</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>Особые поручения</t>
+        </is>
+      </c>
+      <c r="C961" t="n">
+        <v>1999</v>
+      </c>
+      <c r="D961" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>Борис Акунин</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>Коронация</t>
+        </is>
+      </c>
+      <c r="C962" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D962" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>Борис Акунин</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>Любовник смерти</t>
+        </is>
+      </c>
+      <c r="C963" t="n">
+        <v>2001</v>
+      </c>
+      <c r="D963" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>Борис Акунин</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>Любовница смерти</t>
+        </is>
+      </c>
+      <c r="C964" t="n">
+        <v>2001</v>
+      </c>
+      <c r="D964" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>Борис Акунин</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>Алмазная колесница</t>
+        </is>
+      </c>
+      <c r="C965" t="n">
+        <v>2003</v>
+      </c>
+      <c r="D965" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>Борис Акунин</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>Нефритовые чётки</t>
+        </is>
+      </c>
+      <c r="C966" t="n">
+        <v>2006</v>
+      </c>
+      <c r="D966" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>Борис Акунин</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>Весь мир театр</t>
+        </is>
+      </c>
+      <c r="C967" t="n">
+        <v>2009</v>
+      </c>
+      <c r="D967" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>Борис Акунин</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>Чёрный город</t>
+        </is>
+      </c>
+      <c r="C968" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D968" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>Борис Акунин</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>Планета Вода</t>
+        </is>
+      </c>
+      <c r="C969" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D969" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>Борис Акунин</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Пелагия и белый бульдог</t>
+        </is>
+      </c>
+      <c r="C970" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D970" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>Сергей Лукьяненко</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>Сумеречный дозор</t>
+        </is>
+      </c>
+      <c r="C971" t="n">
+        <v>2003</v>
+      </c>
+      <c r="D971" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>Сергей Лукьяненко</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>Последний дозор</t>
+        </is>
+      </c>
+      <c r="C972" t="n">
+        <v>2005</v>
+      </c>
+      <c r="D972" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>Сергей Лукьяненко</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>Новый дозор</t>
+        </is>
+      </c>
+      <c r="C973" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D973" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>Сергей Лукьяненко</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>Фальшивые зеркала</t>
+        </is>
+      </c>
+      <c r="C974" t="n">
+        <v>1999</v>
+      </c>
+      <c r="D974" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>Сергей Лукьяненко</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>Прозрачные витражи</t>
+        </is>
+      </c>
+      <c r="C975" t="n">
+        <v>2001</v>
+      </c>
+      <c r="D975" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>Сергей Лукьяненко</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>Звёзды — холодные игрушки</t>
+        </is>
+      </c>
+      <c r="C976" t="n">
+        <v>1997</v>
+      </c>
+      <c r="D976" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>Сергей Лукьяненко</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>Спектр</t>
+        </is>
+      </c>
+      <c r="C977" t="n">
+        <v>2002</v>
+      </c>
+      <c r="D977" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>Сергей Лукьяненко</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>Геном</t>
+        </is>
+      </c>
+      <c r="C978" t="n">
+        <v>1999</v>
+      </c>
+      <c r="D978" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>Сергей Лукьяненко</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>Холодные берега</t>
+        </is>
+      </c>
+      <c r="C979" t="n">
+        <v>1999</v>
+      </c>
+      <c r="D979" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>Сергей Лукьяненко</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>Рыцари сорока островов</t>
+        </is>
+      </c>
+      <c r="C980" t="n">
+        <v>1992</v>
+      </c>
+      <c r="D980" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>Анджей Сапковский</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>Сезон гроз</t>
+        </is>
+      </c>
+      <c r="C981" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D981" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>Анджей Сапковский</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>Божьи воины</t>
+        </is>
+      </c>
+      <c r="C982" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D982" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>Анджей Сапковский</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>Свет вечный</t>
+        </is>
+      </c>
+      <c r="C983" t="n">
+        <v>2006</v>
+      </c>
+      <c r="D983" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>Дж. Р. Р. Толкин</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>Неоконченные предания Нуменора и Средиземья</t>
+        </is>
+      </c>
+      <c r="C984" t="n">
+        <v>1980</v>
+      </c>
+      <c r="D984" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>Дж. Р. Р. Толкин</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>Дети Хурина</t>
+        </is>
+      </c>
+      <c r="C985" t="n">
+        <v>2007</v>
+      </c>
+      <c r="D985" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>Дж. Р. Р. Толкин</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>Падение Артура</t>
+        </is>
+      </c>
+      <c r="C986" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D986" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>Дж. Р. Р. Толкин</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>Берен и Лютиэн</t>
+        </is>
+      </c>
+      <c r="C987" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D987" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>Дж. Р. Р. Толкин</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>Падение Гондолина</t>
+        </is>
+      </c>
+      <c r="C988" t="n">
+        <v>2018</v>
+      </c>
+      <c r="D988" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>Дж. Р. Р. Толкин</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>Фермер Джайлс из Хэма</t>
+        </is>
+      </c>
+      <c r="C989" t="n">
+        <v>1949</v>
+      </c>
+      <c r="D989" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>Дж. Р. Р. Толкин</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>Приключения Тома Бомбадила</t>
+        </is>
+      </c>
+      <c r="C990" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D990" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>Джон Стейнбек</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>К востоку от Эдема</t>
+        </is>
+      </c>
+      <c r="C991" t="n">
+        <v>1952</v>
+      </c>
+      <c r="D991" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>Джон Стейнбек</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>Зима тревоги нашей</t>
+        </is>
+      </c>
+      <c r="C992" t="n">
+        <v>1961</v>
+      </c>
+      <c r="D992" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>Джон Стейнбек</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>Квартал Тортилья-Флэт</t>
+        </is>
+      </c>
+      <c r="C993" t="n">
+        <v>1935</v>
+      </c>
+      <c r="D993" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>Джон Стейнбек</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>В битве сомнительной</t>
+        </is>
+      </c>
+      <c r="C994" t="n">
+        <v>1936</v>
+      </c>
+      <c r="D994" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>Джон Стейнбек</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>Благостный четверг</t>
+        </is>
+      </c>
+      <c r="C995" t="n">
+        <v>1954</v>
+      </c>
+      <c r="D995" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>Джон Стейнбек</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>Путешествие с Чарли в поисках Америки</t>
+        </is>
+      </c>
+      <c r="C996" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D996" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>Джон Стейнбек</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>Луна зашла</t>
+        </is>
+      </c>
+      <c r="C997" t="n">
+        <v>1942</v>
+      </c>
+      <c r="D997" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>Джон Стейнбек</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>Золотая чаша</t>
+        </is>
+      </c>
+      <c r="C998" t="n">
+        <v>1929</v>
+      </c>
+      <c r="D998" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>Джон Стейнбек</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>Бродячий автобус</t>
+        </is>
+      </c>
+      <c r="C999" t="n">
+        <v>1947</v>
+      </c>
+      <c r="D999" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>Владимир Набоков</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>Ада, или Радости страсти</t>
+        </is>
+      </c>
+      <c r="C1000" t="n">
+        <v>1969</v>
+      </c>
+      <c r="D1000" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>Владимир Набоков</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>Король, дама, валет</t>
+        </is>
+      </c>
+      <c r="C1001" t="n">
+        <v>1928</v>
+      </c>
+      <c r="D1001" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>Владимир Набоков</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>Подвиг</t>
+        </is>
+      </c>
+      <c r="C1002" t="n">
+        <v>1932</v>
+      </c>
+      <c r="D1002" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>Владимир Набоков</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>Камера обскура</t>
+        </is>
+      </c>
+      <c r="C1003" t="n">
+        <v>1933</v>
+      </c>
+      <c r="D1003" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>Владимир Набоков</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>Отчаяние</t>
+        </is>
+      </c>
+      <c r="C1004" t="n">
+        <v>1934</v>
+      </c>
+      <c r="D1004" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>Владимир Набоков</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>Пнин</t>
+        </is>
+      </c>
+      <c r="C1005" t="n">
+        <v>1957</v>
+      </c>
+      <c r="D1005" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>Владимир Набоков</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>Истинная жизнь Себастьяна Найта</t>
+        </is>
+      </c>
+      <c r="C1006" t="n">
+        <v>1941</v>
+      </c>
+      <c r="D1006" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>Владимир Набоков</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>Под знаком незаконнорождённых</t>
+        </is>
+      </c>
+      <c r="C1007" t="n">
+        <v>1947</v>
+      </c>
+      <c r="D1007" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>Владимир Набоков</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>Прозрачные вещи</t>
+        </is>
+      </c>
+      <c r="C1008" t="n">
+        <v>1972</v>
+      </c>
+      <c r="D1008" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>Томас Манн</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>Лотта в Веймаре</t>
+        </is>
+      </c>
+      <c r="C1009" t="n">
+        <v>1939</v>
+      </c>
+      <c r="D1009" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>Томас Манн</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>Признания авантюриста Феликса Круля</t>
+        </is>
+      </c>
+      <c r="C1010" t="n">
+        <v>1954</v>
+      </c>
+      <c r="D1010" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>Томас Манн</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>Королевское высочество</t>
+        </is>
+      </c>
+      <c r="C1011" t="n">
+        <v>1909</v>
+      </c>
+      <c r="D1011" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>Томас Манн</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>Избранник</t>
+        </is>
+      </c>
+      <c r="C1012" t="n">
+        <v>1951</v>
+      </c>
+      <c r="D1012" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>Томас Манн</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>Марио и волшебник</t>
+        </is>
+      </c>
+      <c r="C1013" t="n">
+        <v>1930</v>
+      </c>
+      <c r="D1013" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>Томас Манн</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>Обманутая</t>
+        </is>
+      </c>
+      <c r="C1014" t="n">
+        <v>1953</v>
+      </c>
+      <c r="D1014" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>Герман Гессе</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>Петер Каменцинд</t>
+        </is>
+      </c>
+      <c r="C1015" t="n">
+        <v>1904</v>
+      </c>
+      <c r="D1015" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>Герман Гессе</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>Гертруда</t>
+        </is>
+      </c>
+      <c r="C1016" t="n">
+        <v>1910</v>
+      </c>
+      <c r="D1016" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>Герман Гессе</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>Росхальде</t>
+        </is>
+      </c>
+      <c r="C1017" t="n">
+        <v>1914</v>
+      </c>
+      <c r="D1017" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>Герман Гессе</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>Паломничество в страну Востока</t>
+        </is>
+      </c>
+      <c r="C1018" t="n">
+        <v>1932</v>
+      </c>
+      <c r="D1018" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>Герман Гессе</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>Клейн и Вагнер</t>
+        </is>
+      </c>
+      <c r="C1019" t="n">
+        <v>1919</v>
+      </c>
+      <c r="D1019" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>Герман Гессе</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>Последнее лето Клингзора</t>
+        </is>
+      </c>
+      <c r="C1020" t="n">
+        <v>1920</v>
+      </c>
+      <c r="D1020" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>Ги де Мопассан</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>Монт-Ориоль</t>
+        </is>
+      </c>
+      <c r="C1021" t="n">
+        <v>1887</v>
+      </c>
+      <c r="D1021" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>Ги де Мопассан</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>Сильна как смерть</t>
+        </is>
+      </c>
+      <c r="C1022" t="n">
+        <v>1889</v>
+      </c>
+      <c r="D1022" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>Ги де Мопассан</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>Наше сердце</t>
+        </is>
+      </c>
+      <c r="C1023" t="n">
+        <v>1890</v>
+      </c>
+      <c r="D1023" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>Ги де Мопассан</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>Дом Телье</t>
+        </is>
+      </c>
+      <c r="C1024" t="n">
+        <v>1881</v>
+      </c>
+      <c r="D1024" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>Ги де Мопассан</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>Мадемуазель Фифи</t>
+        </is>
+      </c>
+      <c r="C1025" t="n">
+        <v>1882</v>
+      </c>
+      <c r="D1025" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>Ги де Мопассан</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>Орля</t>
+        </is>
+      </c>
+      <c r="C1026" t="n">
+        <v>1887</v>
+      </c>
+      <c r="D1026" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>Джейн Остин</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>Нортенгерское аббатство</t>
+        </is>
+      </c>
+      <c r="C1027" t="n">
+        <v>1817</v>
+      </c>
+      <c r="D1027" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>Джейн Остин</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>Леди Сьюзен</t>
+        </is>
+      </c>
+      <c r="C1028" t="n">
+        <v>1871</v>
+      </c>
+      <c r="D1028" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>Джек Лондон</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Время не ждёт</t>
+        </is>
+      </c>
+      <c r="C1029" t="n">
+        <v>1910</v>
+      </c>
+      <c r="D1029" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>Джек Лондон</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>Лунная долина</t>
+        </is>
+      </c>
+      <c r="C1030" t="n">
+        <v>1913</v>
+      </c>
+      <c r="D1030" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>Джек Лондон</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Смок Белью</t>
+        </is>
+      </c>
+      <c r="C1031" t="n">
+        <v>1912</v>
+      </c>
+      <c r="D1031" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>Джек Лондон</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>Межзвёздный скиталец</t>
+        </is>
+      </c>
+      <c r="C1032" t="n">
+        <v>1915</v>
+      </c>
+      <c r="D1032" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>Джек Лондон</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>Джон Ячменное Зерно</t>
+        </is>
+      </c>
+      <c r="C1033" t="n">
+        <v>1913</v>
+      </c>
+      <c r="D1033" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>Джек Лондон</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Люди бездны</t>
+        </is>
+      </c>
+      <c r="C1034" t="n">
+        <v>1903</v>
+      </c>
+      <c r="D1034" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>Джек Лондон</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>Дочь снегов</t>
+        </is>
+      </c>
+      <c r="C1035" t="n">
+        <v>1902</v>
+      </c>
+      <c r="D1035" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>Джек Лондон</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>Маленькая хозяйка большого дома</t>
+        </is>
+      </c>
+      <c r="C1036" t="n">
+        <v>1916</v>
+      </c>
+      <c r="D1036" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>Джек Лондон</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>Сердца трёх</t>
+        </is>
+      </c>
+      <c r="C1037" t="n">
+        <v>1920</v>
+      </c>
+      <c r="D1037" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>Джек Лондон</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>Приключение</t>
+        </is>
+      </c>
+      <c r="C1038" t="n">
+        <v>1911</v>
+      </c>
+      <c r="D1038" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>Марк Твен</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>Простаки за границей</t>
+        </is>
+      </c>
+      <c r="C1039" t="n">
+        <v>1869</v>
+      </c>
+      <c r="D1039" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>Марк Твен</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>Налегке</t>
+        </is>
+      </c>
+      <c r="C1040" t="n">
+        <v>1872</v>
+      </c>
+      <c r="D1040" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>Марк Твен</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>Позолоченный век</t>
+        </is>
+      </c>
+      <c r="C1041" t="n">
+        <v>1873</v>
+      </c>
+      <c r="D1041" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>Марк Твен</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>Жизнь на Миссисипи</t>
+        </is>
+      </c>
+      <c r="C1042" t="n">
+        <v>1883</v>
+      </c>
+      <c r="D1042" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>Марк Твен</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>Простофиля Вильсон</t>
+        </is>
+      </c>
+      <c r="C1043" t="n">
+        <v>1894</v>
+      </c>
+      <c r="D1043" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>Марк Твен</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>Том Сойер за границей</t>
+        </is>
+      </c>
+      <c r="C1044" t="n">
+        <v>1894</v>
+      </c>
+      <c r="D1044" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>Марк Твен</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>Том Сойер — сыщик</t>
+        </is>
+      </c>
+      <c r="C1045" t="n">
+        <v>1896</v>
+      </c>
+      <c r="D1045" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>Марк Твен</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>Таинственный незнакомец</t>
+        </is>
+      </c>
+      <c r="C1046" t="n">
+        <v>1916</v>
+      </c>
+      <c r="D1046" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>Марк Твен</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>Личные воспоминания о Жанне д’Арк</t>
+        </is>
+      </c>
+      <c r="C1047" t="n">
+        <v>1896</v>
+      </c>
+      <c r="D1047" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>Сомерсет Моэм</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>Узорный покров</t>
+        </is>
+      </c>
+      <c r="C1048" t="n">
+        <v>1925</v>
+      </c>
+      <c r="D1048" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>Сомерсет Моэм</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>Рождественские каникулы</t>
+        </is>
+      </c>
+      <c r="C1049" t="n">
+        <v>1939</v>
+      </c>
+      <c r="D1049" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>Сомерсет Моэм</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>Лиза из Ламбета</t>
+        </is>
+      </c>
+      <c r="C1050" t="n">
+        <v>1897</v>
+      </c>
+      <c r="D1050" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>Сомерсет Моэм</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>Эшенден, или Британский агент</t>
+        </is>
+      </c>
+      <c r="C1051" t="n">
+        <v>1928</v>
+      </c>
+      <c r="D1051" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>Сомерсет Моэм</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>Подводя итоги</t>
+        </is>
+      </c>
+      <c r="C1052" t="n">
+        <v>1938</v>
+      </c>
+      <c r="D1052" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>Сомерсет Моэм</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>Дождь</t>
+        </is>
+      </c>
+      <c r="C1053" t="n">
+        <v>1921</v>
+      </c>
+      <c r="D1053" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>Сомерсет Моэм</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>Каталина</t>
+        </is>
+      </c>
+      <c r="C1054" t="n">
+        <v>1948</v>
+      </c>
+      <c r="D1054" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>Курт Воннегут</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>Механическое пианино</t>
+        </is>
+      </c>
+      <c r="C1055" t="n">
+        <v>1952</v>
+      </c>
+      <c r="D1055" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>Курт Воннегут</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>Мать Тьма</t>
+        </is>
+      </c>
+      <c r="C1056" t="n">
+        <v>1961</v>
+      </c>
+      <c r="D1056" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>Курт Воннегут</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>Балаган</t>
+        </is>
+      </c>
+      <c r="C1057" t="n">
+        <v>1976</v>
+      </c>
+      <c r="D1057" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>Курт Воннегут</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>Синяя Борода</t>
+        </is>
+      </c>
+      <c r="C1058" t="n">
+        <v>1987</v>
+      </c>
+      <c r="D1058" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>Курт Воннегут</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>Фокус-покус</t>
+        </is>
+      </c>
+      <c r="C1059" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D1059" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>Курт Воннегут</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>Галапагосы</t>
+        </is>
+      </c>
+      <c r="C1060" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D1060" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>Курт Воннегут</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>Времетрясение</t>
+        </is>
+      </c>
+      <c r="C1061" t="n">
+        <v>1997</v>
+      </c>
+      <c r="D1061" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>Курт Воннегут</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>Тюремная птица</t>
+        </is>
+      </c>
+      <c r="C1062" t="n">
+        <v>1979</v>
+      </c>
+      <c r="D1062" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>Курт Воннегут</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>Дай вам Бог здоровья, мистер Розуотер</t>
+        </is>
+      </c>
+      <c r="C1063" t="n">
+        <v>1965</v>
+      </c>
+      <c r="D1063" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>Джордж Оруэлл</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>Дни в Бирме</t>
+        </is>
+      </c>
+      <c r="C1064" t="n">
+        <v>1934</v>
+      </c>
+      <c r="D1064" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>Джордж Оруэлл</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>Дочь священника</t>
+        </is>
+      </c>
+      <c r="C1065" t="n">
+        <v>1935</v>
+      </c>
+      <c r="D1065" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>Джордж Оруэлл</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>Да здравствует фикус!</t>
+        </is>
+      </c>
+      <c r="C1066" t="n">
+        <v>1936</v>
+      </c>
+      <c r="D1066" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>Джордж Оруэлл</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>Глотнуть воздуха</t>
+        </is>
+      </c>
+      <c r="C1067" t="n">
+        <v>1939</v>
+      </c>
+      <c r="D1067" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>Джордж Оруэлл</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>Дорога на Уиган-Пирс</t>
+        </is>
+      </c>
+      <c r="C1068" t="n">
+        <v>1937</v>
+      </c>
+      <c r="D1068" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>Джордж Оруэлл</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>Фунты лиха в Париже и Лондоне</t>
+        </is>
+      </c>
+      <c r="C1069" t="n">
+        <v>1933</v>
+      </c>
+      <c r="D1069" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>Филип К. Дик</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>Через тёмное стекло</t>
+        </is>
+      </c>
+      <c r="C1070" t="n">
+        <v>1977</v>
+      </c>
+      <c r="D1070" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>Филип К. Дик</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>Помутнение</t>
+        </is>
+      </c>
+      <c r="C1071" t="n">
+        <v>1977</v>
+      </c>
+      <c r="D1071" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>Филип К. Дик</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>VALIS</t>
+        </is>
+      </c>
+      <c r="C1072" t="n">
+        <v>1981</v>
+      </c>
+      <c r="D1072" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>Филип К. Дик</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>Мир, который Джонс создал</t>
+        </is>
+      </c>
+      <c r="C1073" t="n">
+        <v>1956</v>
+      </c>
+      <c r="D1073" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>Филип К. Дик</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>Три стигмата Палмера Элдрича</t>
+        </is>
+      </c>
+      <c r="C1074" t="n">
+        <v>1965</v>
+      </c>
+      <c r="D1074" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>Филип К. Дик</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>Доктор Бладмани</t>
+        </is>
+      </c>
+      <c r="C1075" t="n">
+        <v>1965</v>
+      </c>
+      <c r="D1075" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>Филип К. Дик</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>Глаз в небесах</t>
+        </is>
+      </c>
+      <c r="C1076" t="n">
+        <v>1957</v>
+      </c>
+      <c r="D1076" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>Филип К. Дик</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>Время вне суставов</t>
+        </is>
+      </c>
+      <c r="C1077" t="n">
+        <v>1959</v>
+      </c>
+      <c r="D1077" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>Филип К. Дик</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>Тайм-слип на Марсе</t>
+        </is>
+      </c>
+      <c r="C1078" t="n">
+        <v>1964</v>
+      </c>
+      <c r="D1078" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>Филип К. Дик</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>Лейтесь, слёзы, сказал полицейский</t>
+        </is>
+      </c>
+      <c r="C1079" t="n">
+        <v>1974</v>
+      </c>
+      <c r="D1079" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>Филип К. Дик</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>Игроки с Титана</t>
+        </is>
+      </c>
+      <c r="C1080" t="n">
+        <v>1963</v>
+      </c>
+      <c r="D1080" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>Филип К. Дик</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>Мы вас построим</t>
+        </is>
+      </c>
+      <c r="C1081" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D1081" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>Терри Пратчетт</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>Безумная звезда</t>
+        </is>
+      </c>
+      <c r="C1082" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D1082" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>Терри Пратчетт</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>Вещие сёстры</t>
+        </is>
+      </c>
+      <c r="C1083" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D1083" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>Терри Пратчетт</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>Пирамиды</t>
+        </is>
+      </c>
+      <c r="C1084" t="n">
+        <v>1989</v>
+      </c>
+      <c r="D1084" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>Терри Пратчетт</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>Мрачный Жнец</t>
+        </is>
+      </c>
+      <c r="C1085" t="n">
+        <v>1991</v>
+      </c>
+      <c r="D1085" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>Терри Пратчетт</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>Ведьмы за границей</t>
+        </is>
+      </c>
+      <c r="C1086" t="n">
+        <v>1991</v>
+      </c>
+      <c r="D1086" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>Терри Пратчетт</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>Мелкие боги</t>
+        </is>
+      </c>
+      <c r="C1087" t="n">
+        <v>1992</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>Терри Пратчетт</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>Интересные времена</t>
+        </is>
+      </c>
+      <c r="C1088" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>Терри Пратчетт</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>Санта-Хрякус</t>
+        </is>
+      </c>
+      <c r="C1089" t="n">
+        <v>1996</v>
+      </c>
+      <c r="D1089" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>Терри Пратчетт</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>Пятый элефант</t>
+        </is>
+      </c>
+      <c r="C1090" t="n">
+        <v>1999</v>
+      </c>
+      <c r="D1090" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>Терри Пратчетт</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>Правда</t>
+        </is>
+      </c>
+      <c r="C1091" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D1091" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>Терри Пратчетт</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>Опочтарение</t>
+        </is>
+      </c>
+      <c r="C1092" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D1092" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>Габриэль Гарсиа Маркес</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>Генерал в своём лабиринте</t>
+        </is>
+      </c>
+      <c r="C1093" t="n">
+        <v>1989</v>
+      </c>
+      <c r="D1093" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>Габриэль Гарсиа Маркес</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>О любви и других бесах</t>
+        </is>
+      </c>
+      <c r="C1094" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D1094" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>Габриэль Гарсиа Маркес</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>Недобрый час</t>
+        </is>
+      </c>
+      <c r="C1095" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D1095" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>Габриэль Гарсиа Маркес</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>Вспоминая моих грустных шлюх</t>
+        </is>
+      </c>
+      <c r="C1096" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D1096" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>Габриэль Гарсиа Маркес</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>Жить, чтобы рассказывать о жизни</t>
+        </is>
+      </c>
+      <c r="C1097" t="n">
+        <v>2002</v>
+      </c>
+      <c r="D1097" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>Умберто Эко</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>Таинственное пламя царицы Лоаны</t>
+        </is>
+      </c>
+      <c r="C1098" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D1098" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>Умберто Эко</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>Нулевой номер</t>
+        </is>
+      </c>
+      <c r="C1099" t="n">
+        <v>2015</v>
+      </c>
+      <c r="D1099" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>Милан Кундера</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>Жизнь не здесь</t>
+        </is>
+      </c>
+      <c r="C1100" t="n">
+        <v>1973</v>
+      </c>
+      <c r="D1100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>Милан Кундера</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>Прощальный вальс</t>
+        </is>
+      </c>
+      <c r="C1101" t="n">
+        <v>1976</v>
+      </c>
+      <c r="D1101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>Милан Кундера</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>Медлительность</t>
+        </is>
+      </c>
+      <c r="C1102" t="n">
+        <v>1995</v>
+      </c>
+      <c r="D1102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>Милан Кундера</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>Подлинность</t>
+        </is>
+      </c>
+      <c r="C1103" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D1103" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>Милан Кундера</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>Неведение</t>
+        </is>
+      </c>
+      <c r="C1104" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D1104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>Милан Кундера</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>Праздник незначительности</t>
+        </is>
+      </c>
+      <c r="C1105" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D1105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>Милан Кундера</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>Смешные любови</t>
+        </is>
+      </c>
+      <c r="C1106" t="n">
+        <v>1969</v>
+      </c>
+      <c r="D1106" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>Дэн Браун</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>Происхождение</t>
+        </is>
+      </c>
+      <c r="C1107" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D1107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>Дэн Браун</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>Цифровая крепость</t>
+        </is>
+      </c>
+      <c r="C1108" t="n">
+        <v>1998</v>
+      </c>
+      <c r="D1108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>Дэн Браун</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>Точка обмана</t>
+        </is>
+      </c>
+      <c r="C1109" t="n">
+        <v>2001</v>
+      </c>
+      <c r="D1109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>Нил Гейман</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>Благие знамения</t>
+        </is>
+      </c>
+      <c r="C1110" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D1110" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>Нил Гейман</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>Задверье</t>
+        </is>
+      </c>
+      <c r="C1111" t="n">
+        <v>1996</v>
+      </c>
+      <c r="D1111" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>Нил Гейман</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>Кладбищенская книга</t>
+        </is>
+      </c>
+      <c r="C1112" t="n">
+        <v>2008</v>
+      </c>
+      <c r="D1112" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>Нил Гейман</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>Дети Ананси</t>
+        </is>
+      </c>
+      <c r="C1113" t="n">
+        <v>2005</v>
+      </c>
+      <c r="D1113" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>Нил Гейман</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>Океан в конце дороги</t>
+        </is>
+      </c>
+      <c r="C1114" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D1114" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>Пауло Коэльо</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>Брида</t>
+        </is>
+      </c>
+      <c r="C1115" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D1115" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>Пауло Коэльо</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>Валькирии</t>
+        </is>
+      </c>
+      <c r="C1116" t="n">
+        <v>1992</v>
+      </c>
+      <c r="D1116" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>Пауло Коэльо</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>На берегу Рио-Пьедра села я и заплакала</t>
+        </is>
+      </c>
+      <c r="C1117" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D1117" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>Пауло Коэльо</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>Дьявол и сеньорита Прим</t>
+        </is>
+      </c>
+      <c r="C1118" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D1118" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>Пауло Коэльо</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>Зафир</t>
+        </is>
+      </c>
+      <c r="C1119" t="n">
+        <v>2005</v>
+      </c>
+      <c r="D1119" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>Пауло Коэльо</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>Ведьма с Портобелло</t>
+        </is>
+      </c>
+      <c r="C1120" t="n">
+        <v>2006</v>
+      </c>
+      <c r="D1120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>Пауло Коэльо</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>Победитель остаётся один</t>
+        </is>
+      </c>
+      <c r="C1121" t="n">
+        <v>2008</v>
+      </c>
+      <c r="D1121" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>Пауло Коэльо</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>Алеф</t>
+        </is>
+      </c>
+      <c r="C1122" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D1122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>Пауло Коэльо</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>Рукопись, найденная в Акко</t>
+        </is>
+      </c>
+      <c r="C1123" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D1123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>Пауло Коэльо</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>Адюльтер</t>
+        </is>
+      </c>
+      <c r="C1124" t="n">
+        <v>2014</v>
+      </c>
+      <c r="D1124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>Фрэнсис Скотт Фицджеральд</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>Прекрасные и проклятые</t>
+        </is>
+      </c>
+      <c r="C1125" t="n">
+        <v>1922</v>
+      </c>
+      <c r="D1125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>Фрэнсис Скотт Фицджеральд</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>Последний магнат</t>
+        </is>
+      </c>
+      <c r="C1126" t="n">
+        <v>1941</v>
+      </c>
+      <c r="D1126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>Фрэнсис Скотт Фицджеральд</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>Загадочная история Бенджамина Баттона</t>
+        </is>
+      </c>
+      <c r="C1127" t="n">
+        <v>1922</v>
+      </c>
+      <c r="D1127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>Олдос Хаксли</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>Остров</t>
+        </is>
+      </c>
+      <c r="C1128" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D1128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>Олдос Хаксли</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>Контрапункт</t>
+        </is>
+      </c>
+      <c r="C1129" t="n">
+        <v>1928</v>
+      </c>
+      <c r="D1129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>Олдос Хаксли</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>Желтый Кром</t>
+        </is>
+      </c>
+      <c r="C1130" t="n">
+        <v>1921</v>
+      </c>
+      <c r="D1130" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>Олдос Хаксли</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>Шутовской хоровод</t>
+        </is>
+      </c>
+      <c r="C1131" t="n">
+        <v>1923</v>
+      </c>
+      <c r="D1131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>Олдос Хаксли</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>Слепец в Газе</t>
+        </is>
+      </c>
+      <c r="C1132" t="n">
+        <v>1936</v>
+      </c>
+      <c r="D1132" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>Олдос Хаксли</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>Обезьяна и сущность</t>
+        </is>
+      </c>
+      <c r="C1133" t="n">
+        <v>1948</v>
+      </c>
+      <c r="D1133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>Олдос Хаксли</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>Гений и богиня</t>
+        </is>
+      </c>
+      <c r="C1134" t="n">
+        <v>1955</v>
+      </c>
+      <c r="D1134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>Олдос Хаксли</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>Двери восприятия</t>
+        </is>
+      </c>
+      <c r="C1135" t="n">
+        <v>1954</v>
+      </c>
+      <c r="D1135" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>Уильям Фолкнер</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>Когда я умирала</t>
+        </is>
+      </c>
+      <c r="C1136" t="n">
+        <v>1930</v>
+      </c>
+      <c r="D1136" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>Уильям Фолкнер</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>Святилище</t>
+        </is>
+      </c>
+      <c r="C1137" t="n">
+        <v>1931</v>
+      </c>
+      <c r="D1137" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>Уильям Фолкнер</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>Сарторис</t>
+        </is>
+      </c>
+      <c r="C1138" t="n">
+        <v>1929</v>
+      </c>
+      <c r="D1138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>Уильям Фолкнер</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>Солдатская награда</t>
+        </is>
+      </c>
+      <c r="C1139" t="n">
+        <v>1926</v>
+      </c>
+      <c r="D1139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>Уильям Фолкнер</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>Непобеждённые</t>
+        </is>
+      </c>
+      <c r="C1140" t="n">
+        <v>1938</v>
+      </c>
+      <c r="D1140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>Уильям Фолкнер</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>Деревушка</t>
+        </is>
+      </c>
+      <c r="C1141" t="n">
+        <v>1940</v>
+      </c>
+      <c r="D1141" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>Уильям Фолкнер</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>Осквернитель праха</t>
+        </is>
+      </c>
+      <c r="C1142" t="n">
+        <v>1948</v>
+      </c>
+      <c r="D1142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>Уильям Фолкнер</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>Притча</t>
+        </is>
+      </c>
+      <c r="C1143" t="n">
+        <v>1954</v>
+      </c>
+      <c r="D1143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>Уильям Фолкнер</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>Город</t>
+        </is>
+      </c>
+      <c r="C1144" t="n">
+        <v>1957</v>
+      </c>
+      <c r="D1144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>Уильям Фолкнер</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>Особняк</t>
+        </is>
+      </c>
+      <c r="C1145" t="n">
+        <v>1959</v>
+      </c>
+      <c r="D1145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>Уильям Фолкнер</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>Похитители</t>
+        </is>
+      </c>
+      <c r="C1146" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D1146" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>Уильям Фолкнер</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>Дикие пальмы</t>
+        </is>
+      </c>
+      <c r="C1147" t="n">
+        <v>1939</v>
+      </c>
+      <c r="D1147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>Рэй Брэдбери</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>Смерть — дело одинокое</t>
+        </is>
+      </c>
+      <c r="C1148" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D1148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>Рэй Брэдбери</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>Кладбище для безумцев</t>
+        </is>
+      </c>
+      <c r="C1149" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D1149" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>Рэй Брэдбери</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>Из праха восставшие</t>
+        </is>
+      </c>
+      <c r="C1150" t="n">
+        <v>2001</v>
+      </c>
+      <c r="D1150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>Рэй Брэдбери</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>Лето, прощай</t>
+        </is>
+      </c>
+      <c r="C1151" t="n">
+        <v>2006</v>
+      </c>
+      <c r="D1151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>Рэй Брэдбери</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>Зелёные тени, Белый Кит</t>
+        </is>
+      </c>
+      <c r="C1152" t="n">
+        <v>1992</v>
+      </c>
+      <c r="D1152" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>Артур Кларк</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>Космическая одиссея 2001 года</t>
+        </is>
+      </c>
+      <c r="C1153" t="n">
+        <v>1968</v>
+      </c>
+      <c r="D1153" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>Артур Кларк</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>Город и звёзды</t>
+        </is>
+      </c>
+      <c r="C1154" t="n">
+        <v>1956</v>
+      </c>
+      <c r="D1154" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>Артур Кларк</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>Фонтаны рая</t>
+        </is>
+      </c>
+      <c r="C1155" t="n">
+        <v>1979</v>
+      </c>
+      <c r="D1155" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>Артур Кларк</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>Одиссея-два. 2010</t>
+        </is>
+      </c>
+      <c r="C1156" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D1156" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>Артур Кларк</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>Одиссея три</t>
+        </is>
+      </c>
+      <c r="C1157" t="n">
+        <v>1987</v>
+      </c>
+      <c r="D1157" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>Артур Кларк</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>Последняя Одиссея</t>
+        </is>
+      </c>
+      <c r="C1158" t="n">
+        <v>1997</v>
+      </c>
+      <c r="D1158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>Артур Кларк</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>Лунная пыль</t>
+        </is>
+      </c>
+      <c r="C1159" t="n">
+        <v>1961</v>
+      </c>
+      <c r="D1159" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>Артур Кларк</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>Песни далёкой Земли</t>
+        </is>
+      </c>
+      <c r="C1160" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D1160" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>Артур Кларк</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>Пески Марса</t>
+        </is>
+      </c>
+      <c r="C1161" t="n">
+        <v>1951</v>
+      </c>
+      <c r="D1161" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>Артур Кларк</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>Острова в небе</t>
+        </is>
+      </c>
+      <c r="C1162" t="n">
+        <v>1952</v>
+      </c>
+      <c r="D1162" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>Артур Кларк</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>Рама II</t>
+        </is>
+      </c>
+      <c r="C1163" t="n">
+        <v>1989</v>
+      </c>
+      <c r="D1163" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>Грэм Грин</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>Тихий американец</t>
+        </is>
+      </c>
+      <c r="C1164" t="n">
+        <v>1955</v>
+      </c>
+      <c r="D1164" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>Грэм Грин</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>Наш человек в Гаване</t>
+        </is>
+      </c>
+      <c r="C1165" t="n">
+        <v>1958</v>
+      </c>
+      <c r="D1165" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>Грэм Грин</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>Сила и слава</t>
+        </is>
+      </c>
+      <c r="C1166" t="n">
+        <v>1940</v>
+      </c>
+      <c r="D1166" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>Грэм Грин</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>Суть дела</t>
+        </is>
+      </c>
+      <c r="C1167" t="n">
+        <v>1948</v>
+      </c>
+      <c r="D1167" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>Грэм Грин</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>Конец одного романа</t>
+        </is>
+      </c>
+      <c r="C1168" t="n">
+        <v>1951</v>
+      </c>
+      <c r="D1168" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>Грэм Грин</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>Брайтонский леденец</t>
+        </is>
+      </c>
+      <c r="C1169" t="n">
+        <v>1938</v>
+      </c>
+      <c r="D1169" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>Грэм Грин</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>Третий</t>
+        </is>
+      </c>
+      <c r="C1170" t="n">
+        <v>1949</v>
+      </c>
+      <c r="D1170" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>Грэм Грин</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>Комедианты</t>
+        </is>
+      </c>
+      <c r="C1171" t="n">
+        <v>1966</v>
+      </c>
+      <c r="D1171" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>Грэм Грин</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>Почётный консул</t>
+        </is>
+      </c>
+      <c r="C1172" t="n">
+        <v>1973</v>
+      </c>
+      <c r="D1172" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>Грэм Грин</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>Человеческий фактор</t>
+        </is>
+      </c>
+      <c r="C1173" t="n">
+        <v>1978</v>
+      </c>
+      <c r="D1173" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>Грэм Грин</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>Путешествие с тётушкой</t>
+        </is>
+      </c>
+      <c r="C1174" t="n">
+        <v>1969</v>
+      </c>
+      <c r="D1174" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>Грэм Грин</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>Министерство страха</t>
+        </is>
+      </c>
+      <c r="C1175" t="n">
+        <v>1943</v>
+      </c>
+      <c r="D1175" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>Грэм Грин</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>Стамбульский экспресс</t>
+        </is>
+      </c>
+      <c r="C1176" t="n">
+        <v>1932</v>
+      </c>
+      <c r="D1176" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>Грэм Грин</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>Монсеньор Кихот</t>
+        </is>
+      </c>
+      <c r="C1177" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D1177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>Грэм Грин</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>Десятый человек</t>
+        </is>
+      </c>
+      <c r="C1178" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D1178" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>Фрэнк Герберт</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>Бог-император Дюны</t>
+        </is>
+      </c>
+      <c r="C1179" t="n">
+        <v>1981</v>
+      </c>
+      <c r="D1179" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>Фрэнк Герберт</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>Еретики Дюны</t>
+        </is>
+      </c>
+      <c r="C1180" t="n">
+        <v>1984</v>
+      </c>
+      <c r="D1180" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>Фрэнк Герберт</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>Капитул Дюны</t>
+        </is>
+      </c>
+      <c r="C1181" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D1181" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>Фрэнк Герберт</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>Глаза Хейзенберга</t>
+        </is>
+      </c>
+      <c r="C1182" t="n">
+        <v>1966</v>
+      </c>
+      <c r="D1182" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>Фрэнк Герберт</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>Белая чума</t>
+        </is>
+      </c>
+      <c r="C1183" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D1183" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>Фрэнк Герберт</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>Зелёный мозг</t>
+        </is>
+      </c>
+      <c r="C1184" t="n">
+        <v>1966</v>
+      </c>
+      <c r="D1184" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/themes/books/books.xlsx
+++ b/data/themes/books/books.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="books" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="books" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -547,6 +547,9 @@
       <c r="C8" t="n">
         <v>1841</v>
       </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -607,6 +610,9 @@
       <c r="C12" t="n">
         <v>1840</v>
       </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -622,6 +628,9 @@
       <c r="C13" t="n">
         <v>1840</v>
       </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -652,6 +661,9 @@
       <c r="C15" t="n">
         <v>1838</v>
       </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -787,6 +799,9 @@
       <c r="C24" t="n">
         <v>1835</v>
       </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -832,6 +847,9 @@
       <c r="C27" t="n">
         <v>1862</v>
       </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -847,6 +865,9 @@
       <c r="C28" t="n">
         <v>1852</v>
       </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -862,6 +883,9 @@
       <c r="C29" t="n">
         <v>1856</v>
       </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -877,6 +901,9 @@
       <c r="C30" t="n">
         <v>1859</v>
       </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -892,6 +919,9 @@
       <c r="C31" t="n">
         <v>1860</v>
       </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -922,6 +952,9 @@
       <c r="C33" t="n">
         <v>1877</v>
       </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -952,6 +985,9 @@
       <c r="C35" t="n">
         <v>1847</v>
       </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -967,6 +1003,9 @@
       <c r="C36" t="n">
         <v>1869</v>
       </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -982,6 +1021,9 @@
       <c r="C37" t="n">
         <v>1858</v>
       </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1057,6 +1099,9 @@
       <c r="C42" t="n">
         <v>1875</v>
       </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1087,6 +1132,9 @@
       <c r="C44" t="n">
         <v>1848</v>
       </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1102,6 +1150,9 @@
       <c r="C45" t="n">
         <v>1864</v>
       </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1117,6 +1168,9 @@
       <c r="C46" t="n">
         <v>1846</v>
       </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1132,6 +1186,9 @@
       <c r="C47" t="n">
         <v>1861</v>
       </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1147,6 +1204,9 @@
       <c r="C48" t="n">
         <v>1862</v>
       </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1282,6 +1342,9 @@
       <c r="C57" t="n">
         <v>1891</v>
       </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1297,6 +1360,9 @@
       <c r="C58" t="n">
         <v>1912</v>
       </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1312,6 +1378,9 @@
       <c r="C59" t="n">
         <v>1855</v>
       </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1357,6 +1426,9 @@
       <c r="C62" t="n">
         <v>1901</v>
       </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1372,6 +1444,9 @@
       <c r="C63" t="n">
         <v>1897</v>
       </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1387,6 +1462,9 @@
       <c r="C64" t="n">
         <v>1892</v>
       </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1402,6 +1480,9 @@
       <c r="C65" t="n">
         <v>1899</v>
       </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1432,6 +1513,9 @@
       <c r="C67" t="n">
         <v>1898</v>
       </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1447,6 +1531,9 @@
       <c r="C68" t="n">
         <v>1888</v>
       </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1492,6 +1579,9 @@
       <c r="C71" t="n">
         <v>1883</v>
       </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1522,6 +1612,9 @@
       <c r="C73" t="n">
         <v>1865</v>
       </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1537,6 +1630,9 @@
       <c r="C74" t="n">
         <v>1872</v>
       </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1552,6 +1648,9 @@
       <c r="C75" t="n">
         <v>1873</v>
       </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1567,6 +1666,9 @@
       <c r="C76" t="n">
         <v>1870</v>
       </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1582,6 +1684,9 @@
       <c r="C77" t="n">
         <v>1880</v>
       </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1597,6 +1702,9 @@
       <c r="C78" t="n">
         <v>1889</v>
       </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1612,6 +1720,9 @@
       <c r="C79" t="n">
         <v>1885</v>
       </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1627,6 +1738,9 @@
       <c r="C80" t="n">
         <v>1877</v>
       </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1642,6 +1756,9 @@
       <c r="C81" t="n">
         <v>1873</v>
       </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1657,6 +1774,9 @@
       <c r="C82" t="n">
         <v>1864</v>
       </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1747,6 +1867,9 @@
       <c r="C88" t="n">
         <v>1905</v>
       </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1777,6 +1900,9 @@
       <c r="C90" t="n">
         <v>1925</v>
       </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1792,6 +1918,9 @@
       <c r="C91" t="n">
         <v>1924</v>
       </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1807,6 +1936,9 @@
       <c r="C92" t="n">
         <v>1925</v>
       </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1822,6 +1954,9 @@
       <c r="C93" t="n">
         <v>1915</v>
       </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1867,6 +2002,9 @@
       <c r="C96" t="n">
         <v>1916</v>
       </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1897,6 +2035,9 @@
       <c r="C98" t="n">
         <v>1965</v>
       </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1942,6 +2083,9 @@
       <c r="C101" t="n">
         <v>1977</v>
       </c>
+      <c r="D101" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1957,6 +2101,9 @@
       <c r="C102" t="n">
         <v>1945</v>
       </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2002,6 +2149,9 @@
       <c r="C105" t="n">
         <v>1925</v>
       </c>
+      <c r="D105" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2032,6 +2182,9 @@
       <c r="C107" t="n">
         <v>1925</v>
       </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2047,6 +2200,9 @@
       <c r="C108" t="n">
         <v>1924</v>
       </c>
+      <c r="D108" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2062,6 +2218,9 @@
       <c r="C109" t="n">
         <v>1965</v>
       </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2092,6 +2251,9 @@
       <c r="C111" t="n">
         <v>1928</v>
       </c>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2107,6 +2269,9 @@
       <c r="C112" t="n">
         <v>1932</v>
       </c>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2122,6 +2287,9 @@
       <c r="C113" t="n">
         <v>1956</v>
       </c>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2137,6 +2305,9 @@
       <c r="C114" t="n">
         <v>1959</v>
       </c>
+      <c r="D114" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2152,6 +2323,9 @@
       <c r="C115" t="n">
         <v>1926</v>
       </c>
+      <c r="D115" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2197,6 +2371,9 @@
       <c r="C118" t="n">
         <v>1895</v>
       </c>
+      <c r="D118" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2212,6 +2389,9 @@
       <c r="C119" t="n">
         <v>1895</v>
       </c>
+      <c r="D119" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2227,6 +2407,9 @@
       <c r="C120" t="n">
         <v>1892</v>
       </c>
+      <c r="D120" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2242,6 +2425,9 @@
       <c r="C121" t="n">
         <v>1925</v>
       </c>
+      <c r="D121" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2257,6 +2443,9 @@
       <c r="C122" t="n">
         <v>1943</v>
       </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2272,6 +2461,9 @@
       <c r="C123" t="n">
         <v>1930</v>
       </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2287,6 +2479,9 @@
       <c r="C124" t="n">
         <v>1915</v>
       </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2302,6 +2497,9 @@
       <c r="C125" t="n">
         <v>1900</v>
       </c>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2332,6 +2530,9 @@
       <c r="C127" t="n">
         <v>1911</v>
       </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2347,6 +2548,9 @@
       <c r="C128" t="n">
         <v>1898</v>
       </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2377,6 +2581,9 @@
       <c r="C130" t="n">
         <v>1905</v>
       </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2392,6 +2599,9 @@
       <c r="C131" t="n">
         <v>1896</v>
       </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2422,6 +2632,9 @@
       <c r="C133" t="n">
         <v>1908</v>
       </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2437,6 +2650,9 @@
       <c r="C134" t="n">
         <v>1904</v>
       </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2452,6 +2668,9 @@
       <c r="C135" t="n">
         <v>1907</v>
       </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2467,6 +2686,9 @@
       <c r="C136" t="n">
         <v>1919</v>
       </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2512,6 +2734,9 @@
       <c r="C139" t="n">
         <v>1972</v>
       </c>
+      <c r="D139" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2587,6 +2812,9 @@
       <c r="C144" t="n">
         <v>1935</v>
       </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2602,6 +2830,9 @@
       <c r="C145" t="n">
         <v>1926</v>
       </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2617,6 +2848,9 @@
       <c r="C146" t="n">
         <v>1928</v>
       </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2632,6 +2866,9 @@
       <c r="C147" t="n">
         <v>1940</v>
       </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2647,6 +2884,9 @@
       <c r="C148" t="n">
         <v>1939</v>
       </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2662,6 +2902,9 @@
       <c r="C149" t="n">
         <v>1936</v>
       </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2692,6 +2935,9 @@
       <c r="C151" t="n">
         <v>1936</v>
       </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2707,6 +2953,9 @@
       <c r="C152" t="n">
         <v>1945</v>
       </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2722,6 +2971,9 @@
       <c r="C153" t="n">
         <v>1946</v>
       </c>
+      <c r="D153" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2752,6 +3004,9 @@
       <c r="C155" t="n">
         <v>1969</v>
       </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2767,6 +3022,9 @@
       <c r="C156" t="n">
         <v>1974</v>
       </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2782,6 +3040,9 @@
       <c r="C157" t="n">
         <v>1972</v>
       </c>
+      <c r="D157" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2797,6 +3058,9 @@
       <c r="C158" t="n">
         <v>1973</v>
       </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2812,6 +3076,9 @@
       <c r="C159" t="n">
         <v>1971</v>
       </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2842,6 +3109,9 @@
       <c r="C161" t="n">
         <v>1976</v>
       </c>
+      <c r="D161" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2857,6 +3127,9 @@
       <c r="C162" t="n">
         <v>1968</v>
       </c>
+      <c r="D162" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2872,6 +3145,9 @@
       <c r="C163" t="n">
         <v>1971</v>
       </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2887,6 +3163,9 @@
       <c r="C164" t="n">
         <v>1994</v>
       </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2902,6 +3181,9 @@
       <c r="C165" t="n">
         <v>1976</v>
       </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2917,6 +3199,9 @@
       <c r="C166" t="n">
         <v>1974</v>
       </c>
+      <c r="D166" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2932,6 +3217,9 @@
       <c r="C167" t="n">
         <v>1967</v>
       </c>
+      <c r="D167" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2947,6 +3235,9 @@
       <c r="C168" t="n">
         <v>1970</v>
       </c>
+      <c r="D168" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2977,6 +3268,9 @@
       <c r="C170" t="n">
         <v>1976</v>
       </c>
+      <c r="D170" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2992,6 +3286,9 @@
       <c r="C171" t="n">
         <v>1962</v>
       </c>
+      <c r="D171" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3007,6 +3304,9 @@
       <c r="C172" t="n">
         <v>1973</v>
       </c>
+      <c r="D172" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3022,6 +3322,9 @@
       <c r="C173" t="n">
         <v>1968</v>
       </c>
+      <c r="D173" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3037,6 +3340,9 @@
       <c r="C174" t="n">
         <v>1968</v>
       </c>
+      <c r="D174" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3052,6 +3358,9 @@
       <c r="C175" t="n">
         <v>1963</v>
       </c>
+      <c r="D175" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -3067,6 +3376,9 @@
       <c r="C176" t="n">
         <v>1980</v>
       </c>
+      <c r="D176" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3157,6 +3469,9 @@
       <c r="C182" t="n">
         <v>1962</v>
       </c>
+      <c r="D182" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -3232,6 +3547,9 @@
       <c r="C187" t="n">
         <v>1979</v>
       </c>
+      <c r="D187" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -3262,6 +3580,9 @@
       <c r="C189" t="n">
         <v>1988</v>
       </c>
+      <c r="D189" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -3277,6 +3598,9 @@
       <c r="C190" t="n">
         <v>1965</v>
       </c>
+      <c r="D190" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -3292,6 +3616,9 @@
       <c r="C191" t="n">
         <v>1970</v>
       </c>
+      <c r="D191" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -3307,6 +3634,9 @@
       <c r="C192" t="n">
         <v>1957</v>
       </c>
+      <c r="D192" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -3322,6 +3652,9 @@
       <c r="C193" t="n">
         <v>1963</v>
       </c>
+      <c r="D193" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -3337,6 +3670,9 @@
       <c r="C194" t="n">
         <v>1969</v>
       </c>
+      <c r="D194" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -3367,6 +3703,9 @@
       <c r="C196" t="n">
         <v>1925</v>
       </c>
+      <c r="D196" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -3397,6 +3736,9 @@
       <c r="C198" t="n">
         <v>1923</v>
       </c>
+      <c r="D198" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -3412,6 +3754,9 @@
       <c r="C199" t="n">
         <v>1927</v>
       </c>
+      <c r="D199" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -3427,6 +3772,9 @@
       <c r="C200" t="n">
         <v>1922</v>
       </c>
+      <c r="D200" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -3502,6 +3850,9 @@
       <c r="C205" t="n">
         <v>1929</v>
       </c>
+      <c r="D205" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -3577,6 +3928,9 @@
       <c r="C210" t="n">
         <v>1922</v>
       </c>
+      <c r="D210" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -3592,6 +3946,9 @@
       <c r="C211" t="n">
         <v>1923</v>
       </c>
+      <c r="D211" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -3607,6 +3964,9 @@
       <c r="C212" t="n">
         <v>1935</v>
       </c>
+      <c r="D212" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -3622,6 +3982,9 @@
       <c r="C213" t="n">
         <v>1954</v>
       </c>
+      <c r="D213" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -3652,6 +4015,9 @@
       <c r="C215" t="n">
         <v>1951</v>
       </c>
+      <c r="D215" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -3667,6 +4033,9 @@
       <c r="C216" t="n">
         <v>1938</v>
       </c>
+      <c r="D216" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -3682,6 +4051,9 @@
       <c r="C217" t="n">
         <v>1973</v>
       </c>
+      <c r="D217" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -3697,6 +4069,9 @@
       <c r="C218" t="n">
         <v>1966</v>
       </c>
+      <c r="D218" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -3712,6 +4087,9 @@
       <c r="C219" t="n">
         <v>1972</v>
       </c>
+      <c r="D219" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -3742,6 +4120,9 @@
       <c r="C221" t="n">
         <v>1963</v>
       </c>
+      <c r="D221" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -3757,6 +4138,9 @@
       <c r="C222" t="n">
         <v>1964</v>
       </c>
+      <c r="D222" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -3772,6 +4156,9 @@
       <c r="C223" t="n">
         <v>1968</v>
       </c>
+      <c r="D223" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -3787,6 +4174,9 @@
       <c r="C224" t="n">
         <v>1970</v>
       </c>
+      <c r="D224" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -3802,6 +4192,9 @@
       <c r="C225" t="n">
         <v>1939</v>
       </c>
+      <c r="D225" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -3832,6 +4225,9 @@
       <c r="C227" t="n">
         <v>1858</v>
       </c>
+      <c r="D227" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -3847,6 +4243,9 @@
       <c r="C228" t="n">
         <v>1858</v>
       </c>
+      <c r="D228" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -3862,6 +4261,9 @@
       <c r="C229" t="n">
         <v>1856</v>
       </c>
+      <c r="D229" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -3877,6 +4279,9 @@
       <c r="C230" t="n">
         <v>1792</v>
       </c>
+      <c r="D230" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -3892,6 +4297,9 @@
       <c r="C231" t="n">
         <v>1983</v>
       </c>
+      <c r="D231" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -3937,6 +4345,9 @@
       <c r="C234" t="n">
         <v>1981</v>
       </c>
+      <c r="D234" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -3967,6 +4378,9 @@
       <c r="C236" t="n">
         <v>1975</v>
       </c>
+      <c r="D236" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -3982,6 +4396,9 @@
       <c r="C237" t="n">
         <v>1981</v>
       </c>
+      <c r="D237" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -3997,6 +4414,9 @@
       <c r="C238" t="n">
         <v>1961</v>
       </c>
+      <c r="D238" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -4012,6 +4432,9 @@
       <c r="C239" t="n">
         <v>1980</v>
       </c>
+      <c r="D239" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -4027,6 +4450,9 @@
       <c r="C240" t="n">
         <v>1999</v>
       </c>
+      <c r="D240" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -4042,6 +4468,9 @@
       <c r="C241" t="n">
         <v>1996</v>
       </c>
+      <c r="D241" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -4057,6 +4486,9 @@
       <c r="C242" t="n">
         <v>1992</v>
       </c>
+      <c r="D242" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -4072,6 +4504,9 @@
       <c r="C243" t="n">
         <v>1993</v>
       </c>
+      <c r="D243" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -4087,6 +4522,9 @@
       <c r="C244" t="n">
         <v>2004</v>
       </c>
+      <c r="D244" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -4102,6 +4540,9 @@
       <c r="C245" t="n">
         <v>2006</v>
       </c>
+      <c r="D245" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -4132,6 +4573,9 @@
       <c r="C247" t="n">
         <v>1999</v>
       </c>
+      <c r="D247" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -4162,6 +4606,9 @@
       <c r="C249" t="n">
         <v>1985</v>
       </c>
+      <c r="D249" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -4192,6 +4639,9 @@
       <c r="C251" t="n">
         <v>1996</v>
       </c>
+      <c r="D251" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -4207,6 +4657,9 @@
       <c r="C252" t="n">
         <v>2000</v>
       </c>
+      <c r="D252" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -4222,6 +4675,9 @@
       <c r="C253" t="n">
         <v>2010</v>
       </c>
+      <c r="D253" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -4237,6 +4693,9 @@
       <c r="C254" t="n">
         <v>2006</v>
       </c>
+      <c r="D254" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -4252,6 +4711,9 @@
       <c r="C255" t="n">
         <v>1992</v>
       </c>
+      <c r="D255" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -4267,6 +4729,9 @@
       <c r="C256" t="n">
         <v>1998</v>
       </c>
+      <c r="D256" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -4282,6 +4747,9 @@
       <c r="C257" t="n">
         <v>1998</v>
       </c>
+      <c r="D257" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -4297,6 +4765,9 @@
       <c r="C258" t="n">
         <v>1999</v>
       </c>
+      <c r="D258" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -4327,6 +4798,9 @@
       <c r="C260" t="n">
         <v>1998</v>
       </c>
+      <c r="D260" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -4342,6 +4816,9 @@
       <c r="C261" t="n">
         <v>2005</v>
       </c>
+      <c r="D261" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -4357,6 +4834,9 @@
       <c r="C262" t="n">
         <v>2009</v>
       </c>
+      <c r="D262" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -4372,6 +4852,9 @@
       <c r="C263" t="n">
         <v>2015</v>
       </c>
+      <c r="D263" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -4402,6 +4885,9 @@
       <c r="C265" t="n">
         <v>2000</v>
       </c>
+      <c r="D265" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -4432,6 +4918,9 @@
       <c r="C267" t="n">
         <v>2000</v>
       </c>
+      <c r="D267" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -4447,6 +4936,9 @@
       <c r="C268" t="n">
         <v>1997</v>
       </c>
+      <c r="D268" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -4462,6 +4954,9 @@
       <c r="C269" t="n">
         <v>2005</v>
       </c>
+      <c r="D269" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -4477,6 +4972,9 @@
       <c r="C270" t="n">
         <v>2007</v>
       </c>
+      <c r="D270" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -4492,6 +4990,9 @@
       <c r="C271" t="n">
         <v>1984</v>
       </c>
+      <c r="D271" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -4522,6 +5023,9 @@
       <c r="C273" t="n">
         <v>1972</v>
       </c>
+      <c r="D273" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -4537,6 +5041,9 @@
       <c r="C274" t="n">
         <v>1975</v>
       </c>
+      <c r="D274" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -4552,6 +5059,9 @@
       <c r="C275" t="n">
         <v>1969</v>
       </c>
+      <c r="D275" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -4597,6 +5107,9 @@
       <c r="C278" t="n">
         <v>1928</v>
       </c>
+      <c r="D278" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -4612,6 +5125,9 @@
       <c r="C279" t="n">
         <v>1923</v>
       </c>
+      <c r="D279" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -4627,6 +5143,9 @@
       <c r="C280" t="n">
         <v>1925</v>
       </c>
+      <c r="D280" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -4657,6 +5176,9 @@
       <c r="C282" t="n">
         <v>1955</v>
       </c>
+      <c r="D282" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -4672,6 +5194,9 @@
       <c r="C283" t="n">
         <v>1932</v>
       </c>
+      <c r="D283" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -4687,6 +5212,9 @@
       <c r="C284" t="n">
         <v>1945</v>
       </c>
+      <c r="D284" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -4702,6 +5230,9 @@
       <c r="C285" t="n">
         <v>1939</v>
       </c>
+      <c r="D285" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -4732,6 +5263,9 @@
       <c r="C287" t="n">
         <v>1991</v>
       </c>
+      <c r="D287" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -4747,6 +5281,9 @@
       <c r="C288" t="n">
         <v>1997</v>
       </c>
+      <c r="D288" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -4762,6 +5299,9 @@
       <c r="C289" t="n">
         <v>2013</v>
       </c>
+      <c r="D289" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -4777,6 +5317,9 @@
       <c r="C290" t="n">
         <v>1966</v>
       </c>
+      <c r="D290" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -4792,6 +5335,9 @@
       <c r="C291" t="n">
         <v>1958</v>
       </c>
+      <c r="D291" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -4807,6 +5353,9 @@
       <c r="C292" t="n">
         <v>1970</v>
       </c>
+      <c r="D292" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -4822,6 +5371,9 @@
       <c r="C293" t="n">
         <v>1986</v>
       </c>
+      <c r="D293" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -4837,6 +5389,9 @@
       <c r="C294" t="n">
         <v>1980</v>
       </c>
+      <c r="D294" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -5017,6 +5572,9 @@
       <c r="C306" t="n">
         <v>1749</v>
       </c>
+      <c r="D306" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -5032,6 +5590,9 @@
       <c r="C307" t="n">
         <v>1759</v>
       </c>
+      <c r="D307" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -5062,6 +5623,9 @@
       <c r="C309" t="n">
         <v>1811</v>
       </c>
+      <c r="D309" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -5092,6 +5656,9 @@
       <c r="C311" t="n">
         <v>1817</v>
       </c>
+      <c r="D311" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -5107,6 +5674,9 @@
       <c r="C312" t="n">
         <v>1814</v>
       </c>
+      <c r="D312" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -5137,6 +5707,9 @@
       <c r="C314" t="n">
         <v>1819</v>
       </c>
+      <c r="D314" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -5152,6 +5725,9 @@
       <c r="C315" t="n">
         <v>1817</v>
       </c>
+      <c r="D315" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -5167,6 +5743,9 @@
       <c r="C316" t="n">
         <v>1814</v>
       </c>
+      <c r="D316" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -5182,6 +5761,9 @@
       <c r="C317" t="n">
         <v>1823</v>
       </c>
+      <c r="D317" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -5197,6 +5779,9 @@
       <c r="C318" t="n">
         <v>1812</v>
       </c>
+      <c r="D318" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -5227,6 +5812,9 @@
       <c r="C320" t="n">
         <v>1850</v>
       </c>
+      <c r="D320" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -5287,6 +5875,9 @@
       <c r="C324" t="n">
         <v>1837</v>
       </c>
+      <c r="D324" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -5302,6 +5893,9 @@
       <c r="C325" t="n">
         <v>1839</v>
       </c>
+      <c r="D325" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -5317,6 +5911,9 @@
       <c r="C326" t="n">
         <v>1857</v>
       </c>
+      <c r="D326" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -5377,6 +5974,9 @@
       <c r="C330" t="n">
         <v>1871</v>
       </c>
+      <c r="D330" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -5392,6 +5992,9 @@
       <c r="C331" t="n">
         <v>1891</v>
       </c>
+      <c r="D331" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -5407,6 +6010,9 @@
       <c r="C332" t="n">
         <v>1895</v>
       </c>
+      <c r="D332" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -5422,6 +6028,9 @@
       <c r="C333" t="n">
         <v>1874</v>
       </c>
+      <c r="D333" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -5497,6 +6106,9 @@
       <c r="C338" t="n">
         <v>1888</v>
       </c>
+      <c r="D338" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -5542,6 +6154,9 @@
       <c r="C341" t="n">
         <v>1886</v>
       </c>
+      <c r="D341" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -5557,6 +6172,9 @@
       <c r="C342" t="n">
         <v>1888</v>
       </c>
+      <c r="D342" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -5572,6 +6190,9 @@
       <c r="C343" t="n">
         <v>1889</v>
       </c>
+      <c r="D343" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -5602,6 +6223,9 @@
       <c r="C345" t="n">
         <v>1890</v>
       </c>
+      <c r="D345" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -5662,6 +6286,9 @@
       <c r="C349" t="n">
         <v>1915</v>
       </c>
+      <c r="D349" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -5677,6 +6304,9 @@
       <c r="C350" t="n">
         <v>1893</v>
       </c>
+      <c r="D350" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -5692,6 +6322,9 @@
       <c r="C351" t="n">
         <v>1905</v>
       </c>
+      <c r="D351" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -5737,6 +6370,9 @@
       <c r="C354" t="n">
         <v>1902</v>
       </c>
+      <c r="D354" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -5797,6 +6433,9 @@
       <c r="C358" t="n">
         <v>1896</v>
       </c>
+      <c r="D358" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -5812,6 +6451,9 @@
       <c r="C359" t="n">
         <v>1901</v>
       </c>
+      <c r="D359" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -5917,6 +6559,9 @@
       <c r="C366" t="n">
         <v>1876</v>
       </c>
+      <c r="D366" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -5947,6 +6592,9 @@
       <c r="C368" t="n">
         <v>1908</v>
       </c>
+      <c r="D368" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -5962,6 +6610,9 @@
       <c r="C369" t="n">
         <v>1911</v>
       </c>
+      <c r="D369" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -5977,6 +6628,9 @@
       <c r="C370" t="n">
         <v>1886</v>
       </c>
+      <c r="D370" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -5992,6 +6646,9 @@
       <c r="C371" t="n">
         <v>1905</v>
       </c>
+      <c r="D371" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -6052,6 +6709,9 @@
       <c r="C375" t="n">
         <v>1950</v>
       </c>
+      <c r="D375" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -6067,6 +6727,9 @@
       <c r="C376" t="n">
         <v>1951</v>
       </c>
+      <c r="D376" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -6082,6 +6745,9 @@
       <c r="C377" t="n">
         <v>1942</v>
       </c>
+      <c r="D377" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -6097,6 +6763,9 @@
       <c r="C378" t="n">
         <v>1983</v>
       </c>
+      <c r="D378" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -6112,6 +6781,9 @@
       <c r="C379" t="n">
         <v>1987</v>
       </c>
+      <c r="D379" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -6127,6 +6799,9 @@
       <c r="C380" t="n">
         <v>1989</v>
       </c>
+      <c r="D380" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -6157,6 +6832,9 @@
       <c r="C382" t="n">
         <v>1999</v>
       </c>
+      <c r="D382" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -6172,6 +6850,9 @@
       <c r="C383" t="n">
         <v>1996</v>
       </c>
+      <c r="D383" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -6187,6 +6868,9 @@
       <c r="C384" t="n">
         <v>2002</v>
       </c>
+      <c r="D384" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -6247,6 +6931,9 @@
       <c r="C388" t="n">
         <v>2000</v>
       </c>
+      <c r="D388" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -6262,6 +6949,9 @@
       <c r="C389" t="n">
         <v>2003</v>
       </c>
+      <c r="D389" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -6292,6 +6982,9 @@
       <c r="C391" t="n">
         <v>2007</v>
       </c>
+      <c r="D391" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -6337,6 +7030,9 @@
       <c r="C394" t="n">
         <v>1938</v>
       </c>
+      <c r="D394" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -6397,6 +7093,9 @@
       <c r="C398" t="n">
         <v>1945</v>
       </c>
+      <c r="D398" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -6412,6 +7111,9 @@
       <c r="C399" t="n">
         <v>1915</v>
       </c>
+      <c r="D399" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -6427,6 +7129,9 @@
       <c r="C400" t="n">
         <v>1919</v>
       </c>
+      <c r="D400" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -6457,6 +7162,9 @@
       <c r="C402" t="n">
         <v>1944</v>
       </c>
+      <c r="D402" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -6472,6 +7180,9 @@
       <c r="C403" t="n">
         <v>1930</v>
       </c>
+      <c r="D403" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -6487,6 +7198,9 @@
       <c r="C404" t="n">
         <v>1924</v>
       </c>
+      <c r="D404" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -6502,6 +7216,9 @@
       <c r="C405" t="n">
         <v>1925</v>
       </c>
+      <c r="D405" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -6517,6 +7234,9 @@
       <c r="C406" t="n">
         <v>1927</v>
       </c>
+      <c r="D406" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -6562,6 +7282,9 @@
       <c r="C409" t="n">
         <v>1914</v>
       </c>
+      <c r="D409" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -6577,6 +7300,9 @@
       <c r="C410" t="n">
         <v>1916</v>
       </c>
+      <c r="D410" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -6607,6 +7333,9 @@
       <c r="C412" t="n">
         <v>1928</v>
       </c>
+      <c r="D412" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -6682,6 +7411,9 @@
       <c r="C417" t="n">
         <v>1920</v>
       </c>
+      <c r="D417" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -6712,6 +7444,9 @@
       <c r="C419" t="n">
         <v>1936</v>
       </c>
+      <c r="D419" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -6727,6 +7462,9 @@
       <c r="C420" t="n">
         <v>1949</v>
       </c>
+      <c r="D420" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -6742,6 +7480,9 @@
       <c r="C421" t="n">
         <v>1963</v>
       </c>
+      <c r="D421" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -6757,6 +7498,9 @@
       <c r="C422" t="n">
         <v>1996</v>
       </c>
+      <c r="D422" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -6772,6 +7516,9 @@
       <c r="C423" t="n">
         <v>1989</v>
       </c>
+      <c r="D423" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -6817,6 +7564,9 @@
       <c r="C426" t="n">
         <v>1958</v>
       </c>
+      <c r="D426" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -6847,6 +7597,9 @@
       <c r="C428" t="n">
         <v>1989</v>
       </c>
+      <c r="D428" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -6862,6 +7615,9 @@
       <c r="C429" t="n">
         <v>2005</v>
       </c>
+      <c r="D429" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -6877,6 +7633,9 @@
       <c r="C430" t="n">
         <v>2015</v>
       </c>
+      <c r="D430" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -6922,6 +7681,9 @@
       <c r="C433" t="n">
         <v>1969</v>
       </c>
+      <c r="D433" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -6967,6 +7729,9 @@
       <c r="C436" t="n">
         <v>1934</v>
       </c>
+      <c r="D436" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -6982,6 +7747,9 @@
       <c r="C437" t="n">
         <v>1920</v>
       </c>
+      <c r="D437" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -7057,6 +7825,9 @@
       <c r="C442" t="n">
         <v>1961</v>
       </c>
+      <c r="D442" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -7102,6 +7873,9 @@
       <c r="C445" t="n">
         <v>1972</v>
       </c>
+      <c r="D445" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -7117,6 +7891,9 @@
       <c r="C446" t="n">
         <v>2004</v>
       </c>
+      <c r="D446" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -7162,6 +7939,9 @@
       <c r="C449" t="n">
         <v>1876</v>
       </c>
+      <c r="D449" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -7177,6 +7957,9 @@
       <c r="C450" t="n">
         <v>1884</v>
       </c>
+      <c r="D450" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -7237,6 +8020,9 @@
       <c r="C454" t="n">
         <v>1839</v>
       </c>
+      <c r="D454" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -7267,6 +8053,9 @@
       <c r="C456" t="n">
         <v>1843</v>
       </c>
+      <c r="D456" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -7282,6 +8071,9 @@
       <c r="C457" t="n">
         <v>1842</v>
       </c>
+      <c r="D457" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -7312,6 +8104,9 @@
       <c r="C459" t="n">
         <v>1868</v>
       </c>
+      <c r="D459" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -7327,6 +8122,9 @@
       <c r="C460" t="n">
         <v>1909</v>
       </c>
+      <c r="D460" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -7342,6 +8140,9 @@
       <c r="C461" t="n">
         <v>1906</v>
       </c>
+      <c r="D461" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -7357,6 +8158,9 @@
       <c r="C462" t="n">
         <v>1903</v>
       </c>
+      <c r="D462" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -7372,6 +8176,9 @@
       <c r="C463" t="n">
         <v>1904</v>
       </c>
+      <c r="D463" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -7387,6 +8194,9 @@
       <c r="C464" t="n">
         <v>1908</v>
       </c>
+      <c r="D464" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -7417,6 +8227,9 @@
       <c r="C466" t="n">
         <v>1904</v>
       </c>
+      <c r="D466" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -7447,6 +8260,9 @@
       <c r="C468" t="n">
         <v>1925</v>
       </c>
+      <c r="D468" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -7462,6 +8278,9 @@
       <c r="C469" t="n">
         <v>1900</v>
       </c>
+      <c r="D469" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -7477,6 +8296,9 @@
       <c r="C470" t="n">
         <v>1912</v>
       </c>
+      <c r="D470" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -7507,6 +8329,9 @@
       <c r="C472" t="n">
         <v>1929</v>
       </c>
+      <c r="D472" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -7537,6 +8362,9 @@
       <c r="C474" t="n">
         <v>1926</v>
       </c>
+      <c r="D474" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -7552,6 +8380,9 @@
       <c r="C475" t="n">
         <v>1964</v>
       </c>
+      <c r="D475" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -7567,6 +8398,9 @@
       <c r="C476" t="n">
         <v>1936</v>
       </c>
+      <c r="D476" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -7582,6 +8416,9 @@
       <c r="C477" t="n">
         <v>1937</v>
       </c>
+      <c r="D477" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -7597,6 +8434,9 @@
       <c r="C478" t="n">
         <v>1929</v>
       </c>
+      <c r="D478" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -7612,6 +8452,9 @@
       <c r="C479" t="n">
         <v>1932</v>
       </c>
+      <c r="D479" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -7627,6 +8470,9 @@
       <c r="C480" t="n">
         <v>1936</v>
       </c>
+      <c r="D480" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -7672,6 +8518,9 @@
       <c r="C483" t="n">
         <v>1952</v>
       </c>
+      <c r="D483" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -7687,6 +8536,9 @@
       <c r="C484" t="n">
         <v>1945</v>
       </c>
+      <c r="D484" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -7732,6 +8584,9 @@
       <c r="C487" t="n">
         <v>1953</v>
       </c>
+      <c r="D487" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -7747,6 +8602,9 @@
       <c r="C488" t="n">
         <v>1961</v>
       </c>
+      <c r="D488" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -7792,6 +8650,9 @@
       <c r="C491" t="n">
         <v>1957</v>
       </c>
+      <c r="D491" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -7852,6 +8713,9 @@
       <c r="C495" t="n">
         <v>1959</v>
       </c>
+      <c r="D495" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -7867,6 +8731,9 @@
       <c r="C496" t="n">
         <v>1973</v>
       </c>
+      <c r="D496" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -7912,6 +8779,9 @@
       <c r="C499" t="n">
         <v>1950</v>
       </c>
+      <c r="D499" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -7942,6 +8812,9 @@
       <c r="C501" t="n">
         <v>1951</v>
       </c>
+      <c r="D501" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -7957,6 +8830,9 @@
       <c r="C502" t="n">
         <v>1962</v>
       </c>
+      <c r="D502" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -7972,6 +8848,9 @@
       <c r="C503" t="n">
         <v>1951</v>
       </c>
+      <c r="D503" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -7987,6 +8866,9 @@
       <c r="C504" t="n">
         <v>1950</v>
       </c>
+      <c r="D504" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -8002,6 +8884,9 @@
       <c r="C505" t="n">
         <v>1955</v>
       </c>
+      <c r="D505" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -8017,6 +8902,9 @@
       <c r="C506" t="n">
         <v>1954</v>
       </c>
+      <c r="D506" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -8032,6 +8920,9 @@
       <c r="C507" t="n">
         <v>1972</v>
       </c>
+      <c r="D507" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -8047,6 +8938,9 @@
       <c r="C508" t="n">
         <v>1952</v>
       </c>
+      <c r="D508" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -8062,6 +8956,9 @@
       <c r="C509" t="n">
         <v>1961</v>
       </c>
+      <c r="D509" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -8077,6 +8974,9 @@
       <c r="C510" t="n">
         <v>1959</v>
       </c>
+      <c r="D510" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -8092,6 +8992,9 @@
       <c r="C511" t="n">
         <v>1966</v>
       </c>
+      <c r="D511" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -8122,6 +9025,9 @@
       <c r="C513" t="n">
         <v>1969</v>
       </c>
+      <c r="D513" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -8137,6 +9043,9 @@
       <c r="C514" t="n">
         <v>1976</v>
       </c>
+      <c r="D514" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -8167,6 +9076,9 @@
       <c r="C516" t="n">
         <v>1969</v>
       </c>
+      <c r="D516" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -8182,6 +9094,9 @@
       <c r="C517" t="n">
         <v>1962</v>
       </c>
+      <c r="D517" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -8197,6 +9112,9 @@
       <c r="C518" t="n">
         <v>1968</v>
       </c>
+      <c r="D518" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -8212,6 +9130,9 @@
       <c r="C519" t="n">
         <v>1969</v>
       </c>
+      <c r="D519" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -8227,6 +9148,9 @@
       <c r="C520" t="n">
         <v>1974</v>
       </c>
+      <c r="D520" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -8242,6 +9166,9 @@
       <c r="C521" t="n">
         <v>1968</v>
       </c>
+      <c r="D521" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -8257,6 +9184,9 @@
       <c r="C522" t="n">
         <v>1953</v>
       </c>
+      <c r="D522" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -8272,6 +9202,9 @@
       <c r="C523" t="n">
         <v>1973</v>
       </c>
+      <c r="D523" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -8287,6 +9220,9 @@
       <c r="C524" t="n">
         <v>1984</v>
       </c>
+      <c r="D524" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -8332,6 +9268,9 @@
       <c r="C527" t="n">
         <v>1998</v>
       </c>
+      <c r="D527" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -8347,6 +9286,9 @@
       <c r="C528" t="n">
         <v>2000</v>
       </c>
+      <c r="D528" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -8362,6 +9304,9 @@
       <c r="C529" t="n">
         <v>2005</v>
       </c>
+      <c r="D529" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -8377,6 +9322,9 @@
       <c r="C530" t="n">
         <v>2011</v>
       </c>
+      <c r="D530" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -8452,6 +9400,9 @@
       <c r="C535" t="n">
         <v>1987</v>
       </c>
+      <c r="D535" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -8467,6 +9418,9 @@
       <c r="C536" t="n">
         <v>1978</v>
       </c>
+      <c r="D536" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -8482,6 +9436,9 @@
       <c r="C537" t="n">
         <v>1939</v>
       </c>
+      <c r="D537" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -8497,6 +9454,9 @@
       <c r="C538" t="n">
         <v>1940</v>
       </c>
+      <c r="D538" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -8512,6 +9472,9 @@
       <c r="C539" t="n">
         <v>1953</v>
       </c>
+      <c r="D539" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -8542,6 +9505,9 @@
       <c r="C541" t="n">
         <v>2003</v>
       </c>
+      <c r="D541" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -8572,6 +9538,9 @@
       <c r="C543" t="n">
         <v>2013</v>
       </c>
+      <c r="D543" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -8587,6 +9556,9 @@
       <c r="C544" t="n">
         <v>2009</v>
       </c>
+      <c r="D544" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -8632,6 +9604,9 @@
       <c r="C547" t="n">
         <v>2012</v>
       </c>
+      <c r="D547" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -8662,6 +9637,9 @@
       <c r="C549" t="n">
         <v>2009</v>
       </c>
+      <c r="D549" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -8677,6 +9655,9 @@
       <c r="C550" t="n">
         <v>2010</v>
       </c>
+      <c r="D550" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -8812,6 +9793,9 @@
       <c r="C559" t="n">
         <v>2006</v>
       </c>
+      <c r="D559" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -8827,6 +9811,9 @@
       <c r="C560" t="n">
         <v>2007</v>
       </c>
+      <c r="D560" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -8857,6 +9844,9 @@
       <c r="C562" t="n">
         <v>1664</v>
       </c>
+      <c r="D562" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -8872,6 +9862,9 @@
       <c r="C563" t="n">
         <v>1670</v>
       </c>
+      <c r="D563" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -8902,6 +9895,9 @@
       <c r="C565" t="n">
         <v>1666</v>
       </c>
+      <c r="D565" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -8917,6 +9913,9 @@
       <c r="C566" t="n">
         <v>1673</v>
       </c>
+      <c r="D566" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -8932,6 +9931,9 @@
       <c r="C567" t="n">
         <v>1759</v>
       </c>
+      <c r="D567" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -8947,6 +9949,9 @@
       <c r="C568" t="n">
         <v>1697</v>
       </c>
+      <c r="D568" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -8962,6 +9967,9 @@
       <c r="C569" t="n">
         <v>1830</v>
       </c>
+      <c r="D569" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -8977,6 +9985,9 @@
       <c r="C570" t="n">
         <v>1839</v>
       </c>
+      <c r="D570" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -8992,6 +10003,9 @@
       <c r="C571" t="n">
         <v>1835</v>
       </c>
+      <c r="D571" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -9007,6 +10021,9 @@
       <c r="C572" t="n">
         <v>1833</v>
       </c>
+      <c r="D572" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -9022,6 +10039,9 @@
       <c r="C573" t="n">
         <v>1837</v>
       </c>
+      <c r="D573" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -9052,6 +10072,9 @@
       <c r="C575" t="n">
         <v>1830</v>
       </c>
+      <c r="D575" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -9067,6 +10090,9 @@
       <c r="C576" t="n">
         <v>1838</v>
       </c>
+      <c r="D576" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -9127,6 +10153,9 @@
       <c r="C580" t="n">
         <v>1866</v>
       </c>
+      <c r="D580" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -9142,6 +10171,9 @@
       <c r="C581" t="n">
         <v>1874</v>
       </c>
+      <c r="D581" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -9172,6 +10204,9 @@
       <c r="C583" t="n">
         <v>1844</v>
       </c>
+      <c r="D583" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -9202,6 +10237,9 @@
       <c r="C585" t="n">
         <v>1847</v>
       </c>
+      <c r="D585" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -9217,6 +10255,9 @@
       <c r="C586" t="n">
         <v>1845</v>
       </c>
+      <c r="D586" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -9232,6 +10273,9 @@
       <c r="C587" t="n">
         <v>1847</v>
       </c>
+      <c r="D587" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -9262,6 +10306,9 @@
       <c r="C589" t="n">
         <v>1840</v>
       </c>
+      <c r="D589" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -9277,6 +10324,9 @@
       <c r="C590" t="n">
         <v>1829</v>
       </c>
+      <c r="D590" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -9292,6 +10342,9 @@
       <c r="C591" t="n">
         <v>1857</v>
       </c>
+      <c r="D591" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -9307,6 +10360,9 @@
       <c r="C592" t="n">
         <v>1862</v>
       </c>
+      <c r="D592" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -9322,6 +10378,9 @@
       <c r="C593" t="n">
         <v>1869</v>
       </c>
+      <c r="D593" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -9337,6 +10396,9 @@
       <c r="C594" t="n">
         <v>1881</v>
       </c>
+      <c r="D594" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -9367,6 +10429,9 @@
       <c r="C596" t="n">
         <v>1885</v>
       </c>
+      <c r="D596" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -9397,6 +10462,9 @@
       <c r="C598" t="n">
         <v>1880</v>
       </c>
+      <c r="D598" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -9412,6 +10480,9 @@
       <c r="C599" t="n">
         <v>1884</v>
       </c>
+      <c r="D599" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -9427,6 +10498,9 @@
       <c r="C600" t="n">
         <v>1888</v>
       </c>
+      <c r="D600" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -9442,6 +10516,9 @@
       <c r="C601" t="n">
         <v>1877</v>
       </c>
+      <c r="D601" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -9487,6 +10564,9 @@
       <c r="C604" t="n">
         <v>1867</v>
       </c>
+      <c r="D604" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -9502,6 +10582,9 @@
       <c r="C605" t="n">
         <v>1883</v>
       </c>
+      <c r="D605" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -9517,6 +10600,9 @@
       <c r="C606" t="n">
         <v>1873</v>
       </c>
+      <c r="D606" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -9532,6 +10618,9 @@
       <c r="C607" t="n">
         <v>1872</v>
       </c>
+      <c r="D607" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -9562,6 +10651,9 @@
       <c r="C609" t="n">
         <v>1872</v>
       </c>
+      <c r="D609" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -9637,6 +10729,9 @@
       <c r="C614" t="n">
         <v>1878</v>
       </c>
+      <c r="D614" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -9667,6 +10762,9 @@
       <c r="C616" t="n">
         <v>1913</v>
       </c>
+      <c r="D616" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -9712,6 +10810,9 @@
       <c r="C619" t="n">
         <v>1939</v>
       </c>
+      <c r="D619" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -9727,6 +10828,9 @@
       <c r="C620" t="n">
         <v>1931</v>
       </c>
+      <c r="D620" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -9742,6 +10846,9 @@
       <c r="C621" t="n">
         <v>1942</v>
       </c>
+      <c r="D621" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -9832,6 +10939,9 @@
       <c r="C627" t="n">
         <v>1949</v>
       </c>
+      <c r="D627" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -9847,6 +10957,9 @@
       <c r="C628" t="n">
         <v>1954</v>
       </c>
+      <c r="D628" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -9862,6 +10975,9 @@
       <c r="C629" t="n">
         <v>1907</v>
       </c>
+      <c r="D629" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -9892,6 +11008,9 @@
       <c r="C631" t="n">
         <v>2000</v>
       </c>
+      <c r="D631" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -9907,6 +11026,9 @@
       <c r="C632" t="n">
         <v>1998</v>
       </c>
+      <c r="D632" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -9922,6 +11044,9 @@
       <c r="C633" t="n">
         <v>2002</v>
       </c>
+      <c r="D633" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -9952,6 +11077,9 @@
       <c r="C635" t="n">
         <v>1774</v>
       </c>
+      <c r="D635" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -9967,6 +11095,9 @@
       <c r="C636" t="n">
         <v>1796</v>
       </c>
+      <c r="D636" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -9982,6 +11113,9 @@
       <c r="C637" t="n">
         <v>1809</v>
       </c>
+      <c r="D637" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -10012,6 +11146,9 @@
       <c r="C639" t="n">
         <v>1784</v>
       </c>
+      <c r="D639" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -10042,6 +11179,9 @@
       <c r="C641" t="n">
         <v>1787</v>
       </c>
+      <c r="D641" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -10057,6 +11197,9 @@
       <c r="C642" t="n">
         <v>1816</v>
       </c>
+      <c r="D642" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -10072,6 +11215,9 @@
       <c r="C643" t="n">
         <v>1814</v>
       </c>
+      <c r="D643" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -10087,6 +11233,9 @@
       <c r="C644" t="n">
         <v>1819</v>
       </c>
+      <c r="D644" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -10102,6 +11251,9 @@
       <c r="C645" t="n">
         <v>1819</v>
       </c>
+      <c r="D645" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -10162,6 +11314,9 @@
       <c r="C649" t="n">
         <v>1901</v>
       </c>
+      <c r="D649" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -10177,6 +11332,9 @@
       <c r="C650" t="n">
         <v>1947</v>
       </c>
+      <c r="D650" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -10192,6 +11350,9 @@
       <c r="C651" t="n">
         <v>1912</v>
       </c>
+      <c r="D651" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -10207,6 +11368,9 @@
       <c r="C652" t="n">
         <v>1903</v>
       </c>
+      <c r="D652" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -10222,6 +11386,9 @@
       <c r="C653" t="n">
         <v>1933</v>
       </c>
+      <c r="D653" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -10237,6 +11404,9 @@
       <c r="C654" t="n">
         <v>1927</v>
       </c>
+      <c r="D654" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -10252,6 +11422,9 @@
       <c r="C655" t="n">
         <v>1943</v>
       </c>
+      <c r="D655" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -10267,6 +11440,9 @@
       <c r="C656" t="n">
         <v>1922</v>
       </c>
+      <c r="D656" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -10282,6 +11458,9 @@
       <c r="C657" t="n">
         <v>1919</v>
       </c>
+      <c r="D657" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -10297,6 +11476,9 @@
       <c r="C658" t="n">
         <v>1930</v>
       </c>
+      <c r="D658" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -10312,6 +11494,9 @@
       <c r="C659" t="n">
         <v>1906</v>
       </c>
+      <c r="D659" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -10387,6 +11572,9 @@
       <c r="C664" t="n">
         <v>1919</v>
       </c>
+      <c r="D664" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -10432,6 +11620,9 @@
       <c r="C667" t="n">
         <v>1945</v>
       </c>
+      <c r="D667" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -10462,6 +11653,9 @@
       <c r="C669" t="n">
         <v>1962</v>
       </c>
+      <c r="D669" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -10477,6 +11671,9 @@
       <c r="C670" t="n">
         <v>1959</v>
       </c>
+      <c r="D670" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -10492,6 +11689,9 @@
       <c r="C671" t="n">
         <v>1954</v>
       </c>
+      <c r="D671" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -10507,6 +11707,9 @@
       <c r="C672" t="n">
         <v>1941</v>
       </c>
+      <c r="D672" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -10522,6 +11725,9 @@
       <c r="C673" t="n">
         <v>1963</v>
       </c>
+      <c r="D673" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -10597,6 +11803,9 @@
       <c r="C678" t="n">
         <v>2000</v>
       </c>
+      <c r="D678" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -10612,6 +11821,9 @@
       <c r="C679" t="n">
         <v>1994</v>
       </c>
+      <c r="D679" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -10627,6 +11839,9 @@
       <c r="C680" t="n">
         <v>2010</v>
       </c>
+      <c r="D680" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -10657,6 +11872,9 @@
       <c r="C682" t="n">
         <v>1973</v>
       </c>
+      <c r="D682" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -10672,6 +11890,9 @@
       <c r="C683" t="n">
         <v>1960</v>
       </c>
+      <c r="D683" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -10687,6 +11908,9 @@
       <c r="C684" t="n">
         <v>1995</v>
       </c>
+      <c r="D684" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -10717,6 +11941,9 @@
       <c r="C686" t="n">
         <v>1886</v>
       </c>
+      <c r="D686" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -10732,6 +11959,9 @@
       <c r="C687" t="n">
         <v>1872</v>
       </c>
+      <c r="D687" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -10762,6 +11992,9 @@
       <c r="C689" t="n">
         <v>1899</v>
       </c>
+      <c r="D689" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -10822,6 +12055,9 @@
       <c r="C693" t="n">
         <v>1883</v>
       </c>
+      <c r="D693" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -10837,6 +12073,9 @@
       <c r="C694" t="n">
         <v>1957</v>
       </c>
+      <c r="D694" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -10852,6 +12091,9 @@
       <c r="C695" t="n">
         <v>1979</v>
       </c>
+      <c r="D695" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -10867,6 +12109,9 @@
       <c r="C696" t="n">
         <v>1972</v>
       </c>
+      <c r="D696" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -10882,6 +12127,9 @@
       <c r="C697" t="n">
         <v>1947</v>
       </c>
+      <c r="D697" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -10912,6 +12160,9 @@
       <c r="C699" t="n">
         <v>2011</v>
       </c>
+      <c r="D699" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -10957,6 +12208,9 @@
       <c r="C702" t="n">
         <v>1985</v>
       </c>
+      <c r="D702" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -10987,6 +12241,9 @@
       <c r="C704" t="n">
         <v>1981</v>
       </c>
+      <c r="D704" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -11002,6 +12259,9 @@
       <c r="C705" t="n">
         <v>1975</v>
       </c>
+      <c r="D705" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -11032,6 +12292,9 @@
       <c r="C707" t="n">
         <v>1944</v>
       </c>
+      <c r="D707" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -11047,6 +12310,9 @@
       <c r="C708" t="n">
         <v>1963</v>
       </c>
+      <c r="D708" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -11077,6 +12343,9 @@
       <c r="C710" t="n">
         <v>2003</v>
       </c>
+      <c r="D710" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -11092,6 +12361,9 @@
       <c r="C711" t="n">
         <v>1998</v>
       </c>
+      <c r="D711" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -11107,6 +12379,9 @@
       <c r="C712" t="n">
         <v>1987</v>
       </c>
+      <c r="D712" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -11122,6 +12397,9 @@
       <c r="C713" t="n">
         <v>1996</v>
       </c>
+      <c r="D713" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -11137,6 +12415,9 @@
       <c r="C714" t="n">
         <v>1982</v>
       </c>
+      <c r="D714" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -11152,6 +12433,9 @@
       <c r="C715" t="n">
         <v>2001</v>
       </c>
+      <c r="D715" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -11167,6 +12451,9 @@
       <c r="C716" t="n">
         <v>1933</v>
       </c>
+      <c r="D716" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -11182,6 +12469,9 @@
       <c r="C717" t="n">
         <v>1966</v>
       </c>
+      <c r="D717" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -11302,6 +12592,9 @@
       <c r="C725" t="n">
         <v>1867</v>
       </c>
+      <c r="D725" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -11332,6 +12625,9 @@
       <c r="C727" t="n">
         <v>1890</v>
       </c>
+      <c r="D727" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -11347,6 +12643,9 @@
       <c r="C728" t="n">
         <v>1884</v>
       </c>
+      <c r="D728" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
@@ -11392,6 +12691,9 @@
       <c r="C731" t="n">
         <v>1917</v>
       </c>
+      <c r="D731" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
@@ -11407,6 +12709,9 @@
       <c r="C732" t="n">
         <v>1955</v>
       </c>
+      <c r="D732" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
@@ -11422,6 +12727,9 @@
       <c r="C733" t="n">
         <v>1945</v>
       </c>
+      <c r="D733" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
@@ -11437,6 +12745,9 @@
       <c r="C734" t="n">
         <v>1963</v>
       </c>
+      <c r="D734" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
@@ -11452,6 +12763,9 @@
       <c r="C735" t="n">
         <v>1973</v>
       </c>
+      <c r="D735" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
@@ -11467,6 +12781,9 @@
       <c r="C736" t="n">
         <v>1981</v>
       </c>
+      <c r="D736" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
@@ -11482,6 +12799,9 @@
       <c r="C737" t="n">
         <v>1947</v>
       </c>
+      <c r="D737" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
@@ -11497,6 +12817,9 @@
       <c r="C738" t="n">
         <v>1948</v>
       </c>
+      <c r="D738" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
@@ -11512,6 +12835,9 @@
       <c r="C739" t="n">
         <v>1957</v>
       </c>
+      <c r="D739" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
@@ -11527,6 +12853,9 @@
       <c r="C740" t="n">
         <v>1954</v>
       </c>
+      <c r="D740" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
@@ -11557,6 +12886,9 @@
       <c r="C742" t="n">
         <v>2006</v>
       </c>
+      <c r="D742" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
@@ -11572,6 +12904,9 @@
       <c r="C743" t="n">
         <v>2007</v>
       </c>
+      <c r="D743" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
@@ -11602,6 +12937,9 @@
       <c r="C745" t="n">
         <v>1991</v>
       </c>
+      <c r="D745" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
@@ -11632,6 +12970,9 @@
       <c r="C747" t="n">
         <v>1982</v>
       </c>
+      <c r="D747" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
@@ -11647,6 +12988,9 @@
       <c r="C748" t="n">
         <v>2002</v>
       </c>
+      <c r="D748" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
@@ -11662,6 +13006,9 @@
       <c r="C749" t="n">
         <v>2009</v>
       </c>
+      <c r="D749" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
@@ -11677,6 +13024,9 @@
       <c r="C750" t="n">
         <v>1985</v>
       </c>
+      <c r="D750" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
@@ -11692,6 +13042,9 @@
       <c r="C751" t="n">
         <v>1994</v>
       </c>
+      <c r="D751" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
@@ -11707,6 +13060,9 @@
       <c r="C752" t="n">
         <v>1979</v>
       </c>
+      <c r="D752" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
@@ -11722,6 +13078,9 @@
       <c r="C753" t="n">
         <v>1962</v>
       </c>
+      <c r="D753" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
@@ -11737,6 +13096,9 @@
       <c r="C754" t="n">
         <v>1948</v>
       </c>
+      <c r="D754" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
@@ -11752,6 +13114,9 @@
       <c r="C755" t="n">
         <v>1915</v>
       </c>
+      <c r="D755" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
@@ -11797,6 +13162,9 @@
       <c r="C758" t="n">
         <v>2003</v>
       </c>
+      <c r="D758" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
@@ -11812,6 +13180,9 @@
       <c r="C759" t="n">
         <v>1998</v>
       </c>
+      <c r="D759" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
@@ -11842,6 +13213,9 @@
       <c r="C761" t="n">
         <v>2008</v>
       </c>
+      <c r="D761" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
@@ -11857,6 +13231,9 @@
       <c r="C762" t="n">
         <v>1896</v>
       </c>
+      <c r="D762" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
@@ -11872,6 +13249,9 @@
       <c r="C763" t="n">
         <v>1884</v>
       </c>
+      <c r="D763" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
@@ -11917,6 +13297,9 @@
       <c r="C766" t="n">
         <v>1911</v>
       </c>
+      <c r="D766" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
@@ -11962,6 +13345,9 @@
       <c r="C769" t="n">
         <v>1957</v>
       </c>
+      <c r="D769" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
@@ -11977,6 +13363,9 @@
       <c r="C770" t="n">
         <v>1971</v>
       </c>
+      <c r="D770" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
@@ -11992,6 +13381,9 @@
       <c r="C771" t="n">
         <v>1961</v>
       </c>
+      <c r="D771" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
@@ -12007,6 +13399,9 @@
       <c r="C772" t="n">
         <v>1965</v>
       </c>
+      <c r="D772" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
@@ -12022,6 +13417,9 @@
       <c r="C773" t="n">
         <v>1993</v>
       </c>
+      <c r="D773" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
@@ -12037,6 +13435,9 @@
       <c r="C774" t="n">
         <v>1992</v>
       </c>
+      <c r="D774" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
@@ -12052,6 +13453,9 @@
       <c r="C775" t="n">
         <v>1994</v>
       </c>
+      <c r="D775" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
@@ -12067,6 +13471,9 @@
       <c r="C776" t="n">
         <v>1995</v>
       </c>
+      <c r="D776" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
@@ -12082,6 +13489,9 @@
       <c r="C777" t="n">
         <v>1996</v>
       </c>
+      <c r="D777" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
@@ -12097,6 +13507,9 @@
       <c r="C778" t="n">
         <v>1997</v>
       </c>
+      <c r="D778" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
@@ -12112,6 +13525,9 @@
       <c r="C779" t="n">
         <v>1999</v>
       </c>
+      <c r="D779" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
@@ -12142,6 +13558,9 @@
       <c r="C781" t="n">
         <v>1920</v>
       </c>
+      <c r="D781" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
@@ -12157,6 +13576,9 @@
       <c r="C782" t="n">
         <v>1984</v>
       </c>
+      <c r="D782" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
@@ -12202,6 +13624,9 @@
       <c r="C785" t="n">
         <v>1979</v>
       </c>
+      <c r="D785" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
@@ -12217,6 +13642,9 @@
       <c r="C786" t="n">
         <v>1971</v>
       </c>
+      <c r="D786" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
@@ -12232,6 +13660,9 @@
       <c r="C787" t="n">
         <v>1946</v>
       </c>
+      <c r="D787" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
@@ -12247,6 +13678,9 @@
       <c r="C788" t="n">
         <v>1946</v>
       </c>
+      <c r="D788" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -12262,6 +13696,9 @@
       <c r="C789" t="n">
         <v>1936</v>
       </c>
+      <c r="D789" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
@@ -12277,6 +13714,9 @@
       <c r="C790" t="n">
         <v>1989</v>
       </c>
+      <c r="D790" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
@@ -12292,6 +13732,9 @@
       <c r="C791" t="n">
         <v>1997</v>
       </c>
+      <c r="D791" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
@@ -12307,6 +13750,9 @@
       <c r="C792" t="n">
         <v>1937</v>
       </c>
+      <c r="D792" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
@@ -12337,6 +13783,9 @@
       <c r="C794" t="n">
         <v>1976</v>
       </c>
+      <c r="D794" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
@@ -12367,6 +13816,9 @@
       <c r="C796" t="n">
         <v>2011</v>
       </c>
+      <c r="D796" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
@@ -12382,6 +13834,9 @@
       <c r="C797" t="n">
         <v>2011</v>
       </c>
+      <c r="D797" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
@@ -12412,6 +13867,9 @@
       <c r="C799" t="n">
         <v>1956</v>
       </c>
+      <c r="D799" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
@@ -12427,6 +13885,9 @@
       <c r="C800" t="n">
         <v>1972</v>
       </c>
+      <c r="D800" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
@@ -12441,6 +13902,9 @@
       </c>
       <c r="C801" t="n">
         <v>1948</v>
+      </c>
+      <c r="D801" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="802">
